--- a/Overture-Match-Suggestions/CM.xlsx
+++ b/Overture-Match-Suggestions/CM.xlsx
@@ -657,10 +657,22 @@
           <t>AdamawaCameroon</t>
         </is>
       </c>
-      <c r="M2" s="2" t="n"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="n"/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>CM-AD</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Ngaoundéré II</t>
+        </is>
+      </c>
       <c r="Q2" s="2" t="n"/>
       <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
@@ -765,10 +777,22 @@
           <t>AdamawaCameroon</t>
         </is>
       </c>
-      <c r="M3" s="2" t="n"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
-      <c r="P3" s="2" t="n"/>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>CM-AD</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Ngaoundéré I</t>
+        </is>
+      </c>
       <c r="Q3" s="2" t="n"/>
       <c r="R3" s="2" t="n"/>
       <c r="S3" s="2" t="n"/>
@@ -873,10 +897,22 @@
           <t>AdamawaCameroon</t>
         </is>
       </c>
-      <c r="M4" s="2" t="n"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n"/>
-      <c r="P4" s="2" t="n"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>CM-AD</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Ngaoundéré III</t>
+        </is>
+      </c>
       <c r="Q4" s="2" t="n"/>
       <c r="R4" s="2" t="n"/>
       <c r="S4" s="2" t="n"/>
@@ -975,10 +1011,22 @@
           <t>AdamawaCameroon</t>
         </is>
       </c>
-      <c r="M5" s="2" t="n"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="n"/>
-      <c r="P5" s="2" t="n"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>CM-AD</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Banyo</t>
+        </is>
+      </c>
       <c r="Q5" s="2" t="n"/>
       <c r="R5" s="2" t="n"/>
       <c r="S5" s="2" t="n"/>
@@ -1077,10 +1125,22 @@
           <t>AdamawaCameroon</t>
         </is>
       </c>
-      <c r="M6" s="2" t="n"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>CM-AD</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Meiganga</t>
+        </is>
+      </c>
       <c r="Q6" s="2" t="n"/>
       <c r="R6" s="2" t="n"/>
       <c r="S6" s="2" t="n"/>
@@ -1179,10 +1239,22 @@
           <t>AdamawaCameroon</t>
         </is>
       </c>
-      <c r="M7" s="2" t="n"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="n"/>
-      <c r="O7" s="2" t="n"/>
-      <c r="P7" s="2" t="n"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>CM-AD</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Tibati</t>
+        </is>
+      </c>
       <c r="Q7" s="2" t="n"/>
       <c r="R7" s="2" t="n"/>
       <c r="S7" s="2" t="n"/>
@@ -1281,10 +1353,22 @@
           <t>AdamawaCameroon</t>
         </is>
       </c>
-      <c r="M8" s="2" t="n"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="n"/>
-      <c r="O8" s="2" t="n"/>
-      <c r="P8" s="2" t="n"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>CM-AD</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Bankim</t>
+        </is>
+      </c>
       <c r="Q8" s="2" t="n"/>
       <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="n"/>
@@ -1383,10 +1467,22 @@
           <t>AdamawaCameroon</t>
         </is>
       </c>
-      <c r="M9" s="2" t="n"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="n"/>
-      <c r="O9" s="2" t="n"/>
-      <c r="P9" s="2" t="n"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>CM-AD</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Ngaoundal</t>
+        </is>
+      </c>
       <c r="Q9" s="2" t="n"/>
       <c r="R9" s="2" t="n"/>
       <c r="S9" s="2" t="n"/>
@@ -1485,10 +1581,22 @@
           <t>AdamawaCameroon</t>
         </is>
       </c>
-      <c r="M10" s="2" t="n"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>CM-AD</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Bélel</t>
+        </is>
+      </c>
       <c r="Q10" s="2" t="n"/>
       <c r="R10" s="2" t="n"/>
       <c r="S10" s="2" t="n"/>
@@ -1587,10 +1695,22 @@
           <t>AdamawaCameroon</t>
         </is>
       </c>
-      <c r="M11" s="2" t="n"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="n"/>
-      <c r="O11" s="2" t="n"/>
-      <c r="P11" s="2" t="n"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>CM-AD</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Dir</t>
+        </is>
+      </c>
       <c r="Q11" s="2" t="n"/>
       <c r="R11" s="2" t="n"/>
       <c r="S11" s="2" t="n"/>
@@ -1689,10 +1809,22 @@
           <t>AdamawaCameroon</t>
         </is>
       </c>
-      <c r="M12" s="2" t="n"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="n"/>
-      <c r="P12" s="2" t="n"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>CM-AD</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Tignère</t>
+        </is>
+      </c>
       <c r="Q12" s="2" t="n"/>
       <c r="R12" s="2" t="n"/>
       <c r="S12" s="2" t="n"/>
@@ -1791,10 +1923,22 @@
           <t>AdamawaCameroon</t>
         </is>
       </c>
-      <c r="M13" s="2" t="n"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="n"/>
-      <c r="O13" s="2" t="n"/>
-      <c r="P13" s="2" t="n"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>CM-AD</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Nyambaka</t>
+        </is>
+      </c>
       <c r="Q13" s="2" t="n"/>
       <c r="R13" s="2" t="n"/>
       <c r="S13" s="2" t="n"/>
@@ -1893,10 +2037,22 @@
           <t>AdamawaCameroon</t>
         </is>
       </c>
-      <c r="M14" s="3" t="n"/>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N14" s="3" t="n"/>
-      <c r="O14" s="3" t="n"/>
-      <c r="P14" s="3" t="n"/>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>CM-AD</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Ngan'ha</t>
+        </is>
+      </c>
       <c r="Q14" s="3" t="n"/>
       <c r="R14" s="3" t="n"/>
       <c r="S14" s="3" t="n"/>
@@ -1995,10 +2151,22 @@
           <t>AdamawaCameroon</t>
         </is>
       </c>
-      <c r="M15" s="2" t="n"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="n"/>
-      <c r="O15" s="2" t="n"/>
-      <c r="P15" s="2" t="n"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>CM-AD</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Galim-Tignère</t>
+        </is>
+      </c>
       <c r="Q15" s="2" t="n"/>
       <c r="R15" s="2" t="n"/>
       <c r="S15" s="2" t="n"/>
@@ -2097,10 +2265,22 @@
           <t>AdamawaCameroon</t>
         </is>
       </c>
-      <c r="M16" s="2" t="n"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="n"/>
-      <c r="O16" s="2" t="n"/>
-      <c r="P16" s="2" t="n"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>CM-AD</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Martap</t>
+        </is>
+      </c>
       <c r="Q16" s="2" t="n"/>
       <c r="R16" s="2" t="n"/>
       <c r="S16" s="2" t="n"/>
@@ -2199,10 +2379,22 @@
           <t>AdamawaCameroon</t>
         </is>
       </c>
-      <c r="M17" s="2" t="n"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="n"/>
-      <c r="O17" s="2" t="n"/>
-      <c r="P17" s="2" t="n"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>CM-AD</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Djohong</t>
+        </is>
+      </c>
       <c r="Q17" s="2" t="n"/>
       <c r="R17" s="2" t="n"/>
       <c r="S17" s="2" t="n"/>
@@ -2301,10 +2493,22 @@
           <t>AdamawaCameroon</t>
         </is>
       </c>
-      <c r="M18" s="2" t="n"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="n"/>
-      <c r="O18" s="2" t="n"/>
-      <c r="P18" s="2" t="n"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>CM-AD</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Ngaoui</t>
+        </is>
+      </c>
       <c r="Q18" s="2" t="n"/>
       <c r="R18" s="2" t="n"/>
       <c r="S18" s="2" t="n"/>
@@ -2403,10 +2607,22 @@
           <t>AdamawaCameroon</t>
         </is>
       </c>
-      <c r="M19" s="2" t="n"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="n"/>
-      <c r="O19" s="2" t="n"/>
-      <c r="P19" s="2" t="n"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>CM-AD</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Mayo-Darlé</t>
+        </is>
+      </c>
       <c r="Q19" s="2" t="n"/>
       <c r="R19" s="2" t="n"/>
       <c r="S19" s="2" t="n"/>
@@ -2505,10 +2721,22 @@
           <t>AdamawaCameroon</t>
         </is>
       </c>
-      <c r="M20" s="2" t="n"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="n"/>
-      <c r="O20" s="2" t="n"/>
-      <c r="P20" s="2" t="n"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>CM-AD</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Mbé</t>
+        </is>
+      </c>
       <c r="Q20" s="2" t="n"/>
       <c r="R20" s="2" t="n"/>
       <c r="S20" s="2" t="n"/>
@@ -2607,10 +2835,22 @@
           <t>AdamawaCameroon</t>
         </is>
       </c>
-      <c r="M21" s="2" t="n"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="n"/>
-      <c r="O21" s="2" t="n"/>
-      <c r="P21" s="2" t="n"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>CM-AD</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Mayo-Baléo</t>
+        </is>
+      </c>
       <c r="Q21" s="2" t="n"/>
       <c r="R21" s="2" t="n"/>
       <c r="S21" s="2" t="n"/>
@@ -2709,10 +2949,22 @@
           <t>AdamawaCameroon</t>
         </is>
       </c>
-      <c r="M22" s="2" t="n"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="n"/>
-      <c r="O22" s="2" t="n"/>
-      <c r="P22" s="2" t="n"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>CM-AD</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>Kontcha</t>
+        </is>
+      </c>
       <c r="Q22" s="2" t="n"/>
       <c r="R22" s="2" t="n"/>
       <c r="S22" s="2" t="n"/>
@@ -2817,10 +3069,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M23" s="2" t="n"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="n"/>
-      <c r="O23" s="2" t="n"/>
-      <c r="P23" s="2" t="n"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>Bafia</t>
+        </is>
+      </c>
       <c r="Q23" s="2" t="n"/>
       <c r="R23" s="2" t="n"/>
       <c r="S23" s="2" t="n"/>
@@ -2925,10 +3189,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M24" s="2" t="n"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2" t="n"/>
-      <c r="P24" s="2" t="n"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>Yaoundé IV</t>
+        </is>
+      </c>
       <c r="Q24" s="2" t="n"/>
       <c r="R24" s="2" t="n"/>
       <c r="S24" s="2" t="n"/>
@@ -3033,10 +3309,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M25" s="2" t="n"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="n"/>
-      <c r="O25" s="2" t="n"/>
-      <c r="P25" s="2" t="n"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>Yaoundé I</t>
+        </is>
+      </c>
       <c r="Q25" s="2" t="n"/>
       <c r="R25" s="2" t="n"/>
       <c r="S25" s="2" t="n"/>
@@ -3141,10 +3429,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M26" s="2" t="n"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="n"/>
-      <c r="O26" s="2" t="n"/>
-      <c r="P26" s="2" t="n"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>Yaoundé VI</t>
+        </is>
+      </c>
       <c r="Q26" s="2" t="n"/>
       <c r="R26" s="2" t="n"/>
       <c r="S26" s="2" t="n"/>
@@ -3249,10 +3549,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M27" s="2" t="n"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="n"/>
-      <c r="O27" s="2" t="n"/>
-      <c r="P27" s="2" t="n"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>Yaoundé V</t>
+        </is>
+      </c>
       <c r="Q27" s="2" t="n"/>
       <c r="R27" s="2" t="n"/>
       <c r="S27" s="2" t="n"/>
@@ -3357,10 +3669,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M28" s="2" t="n"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="n"/>
-      <c r="O28" s="2" t="n"/>
-      <c r="P28" s="2" t="n"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>Yaoundé III</t>
+        </is>
+      </c>
       <c r="Q28" s="2" t="n"/>
       <c r="R28" s="2" t="n"/>
       <c r="S28" s="2" t="n"/>
@@ -3465,10 +3789,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M29" s="2" t="n"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="n"/>
-      <c r="O29" s="2" t="n"/>
-      <c r="P29" s="2" t="n"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>Yaoundé II</t>
+        </is>
+      </c>
       <c r="Q29" s="2" t="n"/>
       <c r="R29" s="2" t="n"/>
       <c r="S29" s="2" t="n"/>
@@ -3573,10 +3909,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M30" s="2" t="n"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="n"/>
-      <c r="O30" s="2" t="n"/>
-      <c r="P30" s="2" t="n"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>Yaoundé VII</t>
+        </is>
+      </c>
       <c r="Q30" s="2" t="n"/>
       <c r="R30" s="2" t="n"/>
       <c r="S30" s="2" t="n"/>
@@ -3681,10 +4029,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M31" s="2" t="n"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="n"/>
-      <c r="O31" s="2" t="n"/>
-      <c r="P31" s="2" t="n"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>Obala</t>
+        </is>
+      </c>
       <c r="Q31" s="2" t="n"/>
       <c r="R31" s="2" t="n"/>
       <c r="S31" s="2" t="n"/>
@@ -3789,10 +4149,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M32" s="2" t="n"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="n"/>
-      <c r="O32" s="2" t="n"/>
-      <c r="P32" s="2" t="n"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>Sa'a</t>
+        </is>
+      </c>
       <c r="Q32" s="2" t="n"/>
       <c r="R32" s="2" t="n"/>
       <c r="S32" s="2" t="n"/>
@@ -3897,10 +4269,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M33" s="2" t="n"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="n"/>
-      <c r="O33" s="2" t="n"/>
-      <c r="P33" s="2" t="n"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>Okola</t>
+        </is>
+      </c>
       <c r="Q33" s="2" t="n"/>
       <c r="R33" s="2" t="n"/>
       <c r="S33" s="2" t="n"/>
@@ -4005,10 +4389,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M34" s="2" t="n"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="n"/>
-      <c r="O34" s="2" t="n"/>
-      <c r="P34" s="2" t="n"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>Mfou</t>
+        </is>
+      </c>
       <c r="Q34" s="2" t="n"/>
       <c r="R34" s="2" t="n"/>
       <c r="S34" s="2" t="n"/>
@@ -4113,10 +4509,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M35" s="2" t="n"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="n"/>
-      <c r="O35" s="2" t="n"/>
-      <c r="P35" s="2" t="n"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>Monatélé</t>
+        </is>
+      </c>
       <c r="Q35" s="2" t="n"/>
       <c r="R35" s="2" t="n"/>
       <c r="S35" s="2" t="n"/>
@@ -4221,10 +4629,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M36" s="2" t="n"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="n"/>
-      <c r="O36" s="2" t="n"/>
-      <c r="P36" s="2" t="n"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>Soa</t>
+        </is>
+      </c>
       <c r="Q36" s="2" t="n"/>
       <c r="R36" s="2" t="n"/>
       <c r="S36" s="2" t="n"/>
@@ -4329,10 +4749,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M37" s="2" t="n"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="n"/>
-      <c r="O37" s="2" t="n"/>
-      <c r="P37" s="2" t="n"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>Ebebda</t>
+        </is>
+      </c>
       <c r="Q37" s="2" t="n"/>
       <c r="R37" s="2" t="n"/>
       <c r="S37" s="2" t="n"/>
@@ -4437,10 +4869,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M38" s="2" t="n"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="n"/>
-      <c r="O38" s="2" t="n"/>
-      <c r="P38" s="2" t="n"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>Evodoula</t>
+        </is>
+      </c>
       <c r="Q38" s="2" t="n"/>
       <c r="R38" s="2" t="n"/>
       <c r="S38" s="2" t="n"/>
@@ -4545,10 +4989,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M39" s="2" t="n"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="n"/>
-      <c r="O39" s="2" t="n"/>
-      <c r="P39" s="2" t="n"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>Esse</t>
+        </is>
+      </c>
       <c r="Q39" s="2" t="n"/>
       <c r="R39" s="2" t="n"/>
       <c r="S39" s="2" t="n"/>
@@ -4653,10 +5109,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M40" s="2" t="n"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="n"/>
-      <c r="O40" s="2" t="n"/>
-      <c r="P40" s="2" t="n"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>Elig-Mfomo</t>
+        </is>
+      </c>
       <c r="Q40" s="2" t="n"/>
       <c r="R40" s="2" t="n"/>
       <c r="S40" s="2" t="n"/>
@@ -4761,10 +5229,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M41" s="2" t="n"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="n"/>
-      <c r="O41" s="2" t="n"/>
-      <c r="P41" s="2" t="n"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>Awaé</t>
+        </is>
+      </c>
       <c r="Q41" s="2" t="n"/>
       <c r="R41" s="2" t="n"/>
       <c r="S41" s="2" t="n"/>
@@ -4869,10 +5349,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M42" s="2" t="n"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="n"/>
-      <c r="O42" s="2" t="n"/>
-      <c r="P42" s="2" t="n"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>Nkolafamba</t>
+        </is>
+      </c>
       <c r="Q42" s="2" t="n"/>
       <c r="R42" s="2" t="n"/>
       <c r="S42" s="2" t="n"/>
@@ -4977,10 +5469,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M43" s="2" t="n"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="n"/>
-      <c r="O43" s="2" t="n"/>
-      <c r="P43" s="2" t="n"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>Lobo</t>
+        </is>
+      </c>
       <c r="Q43" s="2" t="n"/>
       <c r="R43" s="2" t="n"/>
       <c r="S43" s="2" t="n"/>
@@ -5085,10 +5589,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M44" s="2" t="n"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="n"/>
-      <c r="O44" s="2" t="n"/>
-      <c r="P44" s="2" t="n"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>Batchenga</t>
+        </is>
+      </c>
       <c r="Q44" s="2" t="n"/>
       <c r="R44" s="2" t="n"/>
       <c r="S44" s="2" t="n"/>
@@ -5193,10 +5709,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M45" s="4" t="n"/>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N45" s="4" t="n"/>
-      <c r="O45" s="4" t="n"/>
-      <c r="P45" s="4" t="n"/>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P45" s="4" t="inlineStr">
+        <is>
+          <t>Olanguina</t>
+        </is>
+      </c>
       <c r="Q45" s="4" t="n"/>
       <c r="R45" s="4" t="n"/>
       <c r="S45" s="4" t="n"/>
@@ -5271,10 +5799,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M46" s="2" t="n"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="n"/>
-      <c r="O46" s="2" t="n"/>
-      <c r="P46" s="2" t="n"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>Edzendouan</t>
+        </is>
+      </c>
       <c r="Q46" s="2" t="n"/>
       <c r="R46" s="2" t="n"/>
       <c r="S46" s="2" t="n"/>
@@ -5379,10 +5919,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M47" s="2" t="n"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="n"/>
-      <c r="O47" s="2" t="n"/>
-      <c r="P47" s="2" t="n"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>Afanloum</t>
+        </is>
+      </c>
       <c r="Q47" s="2" t="n"/>
       <c r="R47" s="2" t="n"/>
       <c r="S47" s="2" t="n"/>
@@ -5481,10 +6033,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M48" s="2" t="n"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="n"/>
-      <c r="O48" s="2" t="n"/>
-      <c r="P48" s="2" t="n"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>Mbalmayo</t>
+        </is>
+      </c>
       <c r="Q48" s="2" t="n"/>
       <c r="R48" s="2" t="n"/>
       <c r="S48" s="2" t="n"/>
@@ -5583,10 +6147,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M49" s="2" t="n"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="n"/>
-      <c r="O49" s="2" t="n"/>
-      <c r="P49" s="2" t="n"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>Akonolinga</t>
+        </is>
+      </c>
       <c r="Q49" s="2" t="n"/>
       <c r="R49" s="2" t="n"/>
       <c r="S49" s="2" t="n"/>
@@ -5685,10 +6261,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M50" s="2" t="n"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="n"/>
-      <c r="O50" s="2" t="n"/>
-      <c r="P50" s="2" t="n"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>Mbangassina</t>
+        </is>
+      </c>
       <c r="Q50" s="2" t="n"/>
       <c r="R50" s="2" t="n"/>
       <c r="S50" s="2" t="n"/>
@@ -5787,10 +6375,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M51" s="2" t="n"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="n"/>
-      <c r="O51" s="2" t="n"/>
-      <c r="P51" s="2" t="n"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>Bokito</t>
+        </is>
+      </c>
       <c r="Q51" s="2" t="n"/>
       <c r="R51" s="2" t="n"/>
       <c r="S51" s="2" t="n"/>
@@ -5889,10 +6489,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M52" s="2" t="n"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="n"/>
-      <c r="O52" s="2" t="n"/>
-      <c r="P52" s="2" t="n"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>Nanga-Eboko</t>
+        </is>
+      </c>
       <c r="Q52" s="2" t="n"/>
       <c r="R52" s="2" t="n"/>
       <c r="S52" s="2" t="n"/>
@@ -5991,10 +6603,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M53" s="2" t="n"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="n"/>
-      <c r="O53" s="2" t="n"/>
-      <c r="P53" s="2" t="n"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>Makak</t>
+        </is>
+      </c>
       <c r="Q53" s="2" t="n"/>
       <c r="R53" s="2" t="n"/>
       <c r="S53" s="2" t="n"/>
@@ -6093,10 +6717,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M54" s="2" t="n"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="n"/>
-      <c r="O54" s="2" t="n"/>
-      <c r="P54" s="2" t="n"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>Ombessa</t>
+        </is>
+      </c>
       <c r="Q54" s="2" t="n"/>
       <c r="R54" s="2" t="n"/>
       <c r="S54" s="2" t="n"/>
@@ -6195,10 +6831,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M55" s="2" t="n"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="n"/>
-      <c r="O55" s="2" t="n"/>
-      <c r="P55" s="2" t="n"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>Ntui</t>
+        </is>
+      </c>
       <c r="Q55" s="2" t="n"/>
       <c r="R55" s="2" t="n"/>
       <c r="S55" s="2" t="n"/>
@@ -6297,10 +6945,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M56" s="2" t="n"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="n"/>
-      <c r="O56" s="2" t="n"/>
-      <c r="P56" s="2" t="n"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>Éséka</t>
+        </is>
+      </c>
       <c r="Q56" s="2" t="n"/>
       <c r="R56" s="2" t="n"/>
       <c r="S56" s="2" t="n"/>
@@ -6399,10 +7059,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M57" s="2" t="n"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="n"/>
-      <c r="O57" s="2" t="n"/>
-      <c r="P57" s="2" t="n"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>Ayos</t>
+        </is>
+      </c>
       <c r="Q57" s="2" t="n"/>
       <c r="R57" s="2" t="n"/>
       <c r="S57" s="2" t="n"/>
@@ -6501,10 +7173,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M58" s="2" t="n"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="n"/>
-      <c r="O58" s="2" t="n"/>
-      <c r="P58" s="2" t="n"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>Mbandjock</t>
+        </is>
+      </c>
       <c r="Q58" s="2" t="n"/>
       <c r="R58" s="2" t="n"/>
       <c r="S58" s="2" t="n"/>
@@ -6603,10 +7287,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M59" s="2" t="n"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="n"/>
-      <c r="O59" s="2" t="n"/>
-      <c r="P59" s="2" t="n"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>Mbankomo</t>
+        </is>
+      </c>
       <c r="Q59" s="2" t="n"/>
       <c r="R59" s="2" t="n"/>
       <c r="S59" s="2" t="n"/>
@@ -6705,10 +7401,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M60" s="2" t="n"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="n"/>
-      <c r="O60" s="2" t="n"/>
-      <c r="P60" s="2" t="n"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>Nkoteng</t>
+        </is>
+      </c>
       <c r="Q60" s="2" t="n"/>
       <c r="R60" s="2" t="n"/>
       <c r="S60" s="2" t="n"/>
@@ -6807,10 +7515,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M61" s="2" t="n"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="n"/>
-      <c r="O61" s="2" t="n"/>
-      <c r="P61" s="2" t="n"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>Ndikiniméki</t>
+        </is>
+      </c>
       <c r="Q61" s="2" t="n"/>
       <c r="R61" s="2" t="n"/>
       <c r="S61" s="2" t="n"/>
@@ -6909,10 +7629,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M62" s="2" t="n"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="n"/>
-      <c r="O62" s="2" t="n"/>
-      <c r="P62" s="2" t="n"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>Ngomedzap</t>
+        </is>
+      </c>
       <c r="Q62" s="2" t="n"/>
       <c r="R62" s="2" t="n"/>
       <c r="S62" s="2" t="n"/>
@@ -7011,10 +7743,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M63" s="2" t="n"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="n"/>
-      <c r="O63" s="2" t="n"/>
-      <c r="P63" s="2" t="n"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>Bot-Makak</t>
+        </is>
+      </c>
       <c r="Q63" s="2" t="n"/>
       <c r="R63" s="2" t="n"/>
       <c r="S63" s="2" t="n"/>
@@ -7113,10 +7857,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M64" s="2" t="n"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="n"/>
-      <c r="O64" s="2" t="n"/>
-      <c r="P64" s="2" t="n"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>Makenene</t>
+        </is>
+      </c>
       <c r="Q64" s="2" t="n"/>
       <c r="R64" s="2" t="n"/>
       <c r="S64" s="2" t="n"/>
@@ -7215,10 +7971,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M65" s="2" t="n"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="n"/>
-      <c r="O65" s="2" t="n"/>
-      <c r="P65" s="2" t="n"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>Bikok</t>
+        </is>
+      </c>
       <c r="Q65" s="2" t="n"/>
       <c r="R65" s="2" t="n"/>
       <c r="S65" s="2" t="n"/>
@@ -7317,10 +8085,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M66" s="2" t="n"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="n"/>
-      <c r="O66" s="2" t="n"/>
-      <c r="P66" s="2" t="n"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>Endom</t>
+        </is>
+      </c>
       <c r="Q66" s="2" t="n"/>
       <c r="R66" s="2" t="n"/>
       <c r="S66" s="2" t="n"/>
@@ -7419,10 +8199,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M67" s="2" t="n"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="n"/>
-      <c r="O67" s="2" t="n"/>
-      <c r="P67" s="2" t="n"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>Messondo</t>
+        </is>
+      </c>
       <c r="Q67" s="2" t="n"/>
       <c r="R67" s="2" t="n"/>
       <c r="S67" s="2" t="n"/>
@@ -7521,10 +8313,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M68" s="2" t="n"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="n"/>
-      <c r="O68" s="2" t="n"/>
-      <c r="P68" s="2" t="n"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>Ngoumou</t>
+        </is>
+      </c>
       <c r="Q68" s="2" t="n"/>
       <c r="R68" s="2" t="n"/>
       <c r="S68" s="2" t="n"/>
@@ -7623,10 +8427,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M69" s="2" t="n"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="n"/>
-      <c r="O69" s="2" t="n"/>
-      <c r="P69" s="2" t="n"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>Ngoro</t>
+        </is>
+      </c>
       <c r="Q69" s="2" t="n"/>
       <c r="R69" s="2" t="n"/>
       <c r="S69" s="2" t="n"/>
@@ -7797,10 +8613,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M71" s="2" t="n"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="n"/>
-      <c r="O71" s="2" t="n"/>
-      <c r="P71" s="2" t="n"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>Ngambé-Tikar</t>
+        </is>
+      </c>
       <c r="Q71" s="2" t="n"/>
       <c r="R71" s="2" t="n"/>
       <c r="S71" s="2" t="n"/>
@@ -7899,10 +8727,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M72" s="2" t="n"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="n"/>
-      <c r="O72" s="2" t="n"/>
-      <c r="P72" s="2" t="n"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>Yoko</t>
+        </is>
+      </c>
       <c r="Q72" s="2" t="n"/>
       <c r="R72" s="2" t="n"/>
       <c r="S72" s="2" t="n"/>
@@ -8001,10 +8841,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M73" s="2" t="n"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="n"/>
-      <c r="O73" s="2" t="n"/>
-      <c r="P73" s="2" t="n"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>Matomb</t>
+        </is>
+      </c>
       <c r="Q73" s="2" t="n"/>
       <c r="R73" s="2" t="n"/>
       <c r="S73" s="2" t="n"/>
@@ -8103,10 +8955,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M74" s="2" t="n"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="n"/>
-      <c r="O74" s="2" t="n"/>
-      <c r="P74" s="2" t="n"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>Deuk</t>
+        </is>
+      </c>
       <c r="Q74" s="2" t="n"/>
       <c r="R74" s="2" t="n"/>
       <c r="S74" s="2" t="n"/>
@@ -8205,10 +9069,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M75" s="2" t="n"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="n"/>
-      <c r="O75" s="2" t="n"/>
-      <c r="P75" s="2" t="n"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>Minta</t>
+        </is>
+      </c>
       <c r="Q75" s="2" t="n"/>
       <c r="R75" s="2" t="n"/>
       <c r="S75" s="2" t="n"/>
@@ -8379,10 +9255,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M77" s="2" t="n"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="n"/>
-      <c r="O77" s="2" t="n"/>
-      <c r="P77" s="2" t="n"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>Dzeng</t>
+        </is>
+      </c>
       <c r="Q77" s="2" t="n"/>
       <c r="R77" s="2" t="n"/>
       <c r="S77" s="2" t="n"/>
@@ -8481,10 +9369,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M78" s="2" t="n"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="n"/>
-      <c r="O78" s="2" t="n"/>
-      <c r="P78" s="2" t="n"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>Ngog-Mapubi</t>
+        </is>
+      </c>
       <c r="Q78" s="2" t="n"/>
       <c r="R78" s="2" t="n"/>
       <c r="S78" s="2" t="n"/>
@@ -8583,10 +9483,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M79" s="2" t="n"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="n"/>
-      <c r="O79" s="2" t="n"/>
-      <c r="P79" s="2" t="n"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>Dibang</t>
+        </is>
+      </c>
       <c r="Q79" s="2" t="n"/>
       <c r="R79" s="2" t="n"/>
       <c r="S79" s="2" t="n"/>
@@ -8685,10 +9597,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M80" s="2" t="n"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="n"/>
-      <c r="O80" s="2" t="n"/>
-      <c r="P80" s="2" t="n"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>Kon-Yambetta</t>
+        </is>
+      </c>
       <c r="Q80" s="2" t="n"/>
       <c r="R80" s="2" t="n"/>
       <c r="S80" s="2" t="n"/>
@@ -8787,10 +9711,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M81" s="2" t="n"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="n"/>
-      <c r="O81" s="2" t="n"/>
-      <c r="P81" s="2" t="n"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>Kiiki</t>
+        </is>
+      </c>
       <c r="Q81" s="2" t="n"/>
       <c r="R81" s="2" t="n"/>
       <c r="S81" s="2" t="n"/>
@@ -8889,10 +9825,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M82" s="2" t="n"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="n"/>
-      <c r="O82" s="2" t="n"/>
-      <c r="P82" s="2" t="n"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>Akono</t>
+        </is>
+      </c>
       <c r="Q82" s="2" t="n"/>
       <c r="R82" s="2" t="n"/>
       <c r="S82" s="2" t="n"/>
@@ -8991,10 +9939,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M83" s="2" t="n"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="n"/>
-      <c r="O83" s="2" t="n"/>
-      <c r="P83" s="2" t="n"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>Bondjock</t>
+        </is>
+      </c>
       <c r="Q83" s="2" t="n"/>
       <c r="R83" s="2" t="n"/>
       <c r="S83" s="2" t="n"/>
@@ -9093,10 +10053,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M84" s="2" t="n"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="n"/>
-      <c r="O84" s="2" t="n"/>
-      <c r="P84" s="2" t="n"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>Mengang</t>
+        </is>
+      </c>
       <c r="Q84" s="2" t="n"/>
       <c r="R84" s="2" t="n"/>
       <c r="S84" s="2" t="n"/>
@@ -9195,10 +10167,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M85" s="2" t="n"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="n"/>
-      <c r="O85" s="2" t="n"/>
-      <c r="P85" s="2" t="n"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>Mengueme</t>
+        </is>
+      </c>
       <c r="Q85" s="2" t="n"/>
       <c r="R85" s="2" t="n"/>
       <c r="S85" s="2" t="n"/>
@@ -9369,10 +10353,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M87" s="2" t="n"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="n"/>
-      <c r="O87" s="2" t="n"/>
-      <c r="P87" s="2" t="n"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>Nsem</t>
+        </is>
+      </c>
       <c r="Q87" s="2" t="n"/>
       <c r="R87" s="2" t="n"/>
       <c r="S87" s="2" t="n"/>
@@ -9471,10 +10467,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M88" s="2" t="n"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="n"/>
-      <c r="O88" s="2" t="n"/>
-      <c r="P88" s="2" t="n"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>Akoéman</t>
+        </is>
+      </c>
       <c r="Q88" s="2" t="n"/>
       <c r="R88" s="2" t="n"/>
       <c r="S88" s="2" t="n"/>
@@ -9573,10 +10581,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M89" s="2" t="n"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="n"/>
-      <c r="O89" s="2" t="n"/>
-      <c r="P89" s="2" t="n"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>Bibey</t>
+        </is>
+      </c>
       <c r="Q89" s="2" t="n"/>
       <c r="R89" s="2" t="n"/>
       <c r="S89" s="2" t="n"/>
@@ -9675,10 +10695,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M90" s="2" t="n"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="n"/>
-      <c r="O90" s="2" t="n"/>
-      <c r="P90" s="2" t="n"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>Nitoukou</t>
+        </is>
+      </c>
       <c r="Q90" s="2" t="n"/>
       <c r="R90" s="2" t="n"/>
       <c r="S90" s="2" t="n"/>
@@ -9777,10 +10809,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M91" s="2" t="n"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="n"/>
-      <c r="O91" s="2" t="n"/>
-      <c r="P91" s="2" t="n"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>Nguibassal</t>
+        </is>
+      </c>
       <c r="Q91" s="2" t="n"/>
       <c r="R91" s="2" t="n"/>
       <c r="S91" s="2" t="n"/>
@@ -9879,10 +10923,22 @@
           <t>CentralCameroon</t>
         </is>
       </c>
-      <c r="M92" s="2" t="n"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="n"/>
-      <c r="O92" s="2" t="n"/>
-      <c r="P92" s="2" t="n"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>CM-CE</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>Biyouha</t>
+        </is>
+      </c>
       <c r="Q92" s="2" t="n"/>
       <c r="R92" s="2" t="n"/>
       <c r="S92" s="2" t="n"/>
@@ -9981,10 +11037,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M93" s="2" t="n"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="n"/>
-      <c r="O93" s="2" t="n"/>
-      <c r="P93" s="2" t="n"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>Batouri</t>
+        </is>
+      </c>
       <c r="Q93" s="2" t="n"/>
       <c r="R93" s="2" t="n"/>
       <c r="S93" s="2" t="n"/>
@@ -10083,10 +11151,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M94" s="2" t="n"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="n"/>
-      <c r="O94" s="2" t="n"/>
-      <c r="P94" s="2" t="n"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>Yokadouma</t>
+        </is>
+      </c>
       <c r="Q94" s="2" t="n"/>
       <c r="R94" s="2" t="n"/>
       <c r="S94" s="2" t="n"/>
@@ -10185,10 +11265,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M95" s="2" t="n"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="n"/>
-      <c r="O95" s="2" t="n"/>
-      <c r="P95" s="2" t="n"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>Bertoua I</t>
+        </is>
+      </c>
       <c r="Q95" s="2" t="n"/>
       <c r="R95" s="2" t="n"/>
       <c r="S95" s="2" t="n"/>
@@ -10287,10 +11379,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M96" s="2" t="n"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="n"/>
-      <c r="O96" s="2" t="n"/>
-      <c r="P96" s="2" t="n"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>Bertoua II</t>
+        </is>
+      </c>
       <c r="Q96" s="2" t="n"/>
       <c r="R96" s="2" t="n"/>
       <c r="S96" s="2" t="n"/>
@@ -10389,10 +11493,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M97" s="2" t="n"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="n"/>
-      <c r="O97" s="2" t="n"/>
-      <c r="P97" s="2" t="n"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>Garoua-Boulaï</t>
+        </is>
+      </c>
       <c r="Q97" s="2" t="n"/>
       <c r="R97" s="2" t="n"/>
       <c r="S97" s="2" t="n"/>
@@ -10491,10 +11607,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M98" s="2" t="n"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="n"/>
-      <c r="O98" s="2" t="n"/>
-      <c r="P98" s="2" t="n"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>Bétaré-Oya</t>
+        </is>
+      </c>
       <c r="Q98" s="2" t="n"/>
       <c r="R98" s="2" t="n"/>
       <c r="S98" s="2" t="n"/>
@@ -10593,10 +11721,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M99" s="2" t="n"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="n"/>
-      <c r="O99" s="2" t="n"/>
-      <c r="P99" s="2" t="n"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>Ngoura</t>
+        </is>
+      </c>
       <c r="Q99" s="2" t="n"/>
       <c r="R99" s="2" t="n"/>
       <c r="S99" s="2" t="n"/>
@@ -10695,10 +11835,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M100" s="2" t="n"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="n"/>
-      <c r="O100" s="2" t="n"/>
-      <c r="P100" s="2" t="n"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>Kétté</t>
+        </is>
+      </c>
       <c r="Q100" s="2" t="n"/>
       <c r="R100" s="2" t="n"/>
       <c r="S100" s="2" t="n"/>
@@ -10797,10 +11949,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M101" s="2" t="n"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="n"/>
-      <c r="O101" s="2" t="n"/>
-      <c r="P101" s="2" t="n"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>Bélabo</t>
+        </is>
+      </c>
       <c r="Q101" s="2" t="n"/>
       <c r="R101" s="2" t="n"/>
       <c r="S101" s="2" t="n"/>
@@ -10899,10 +12063,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M102" s="2" t="n"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="n"/>
-      <c r="O102" s="2" t="n"/>
-      <c r="P102" s="2" t="n"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>Abong-Mbang</t>
+        </is>
+      </c>
       <c r="Q102" s="2" t="n"/>
       <c r="R102" s="2" t="n"/>
       <c r="S102" s="2" t="n"/>
@@ -11001,10 +12177,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M103" s="2" t="n"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="n"/>
-      <c r="O103" s="2" t="n"/>
-      <c r="P103" s="2" t="n"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>Messaména</t>
+        </is>
+      </c>
       <c r="Q103" s="2" t="n"/>
       <c r="R103" s="2" t="n"/>
       <c r="S103" s="2" t="n"/>
@@ -11103,10 +12291,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M104" s="2" t="n"/>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="n"/>
-      <c r="O104" s="2" t="n"/>
-      <c r="P104" s="2" t="n"/>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>Ndélélé</t>
+        </is>
+      </c>
       <c r="Q104" s="2" t="n"/>
       <c r="R104" s="2" t="n"/>
       <c r="S104" s="2" t="n"/>
@@ -11205,10 +12405,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M105" s="2" t="n"/>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N105" s="2" t="n"/>
-      <c r="O105" s="2" t="n"/>
-      <c r="P105" s="2" t="n"/>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>Mbang</t>
+        </is>
+      </c>
       <c r="Q105" s="2" t="n"/>
       <c r="R105" s="2" t="n"/>
       <c r="S105" s="2" t="n"/>
@@ -11307,10 +12519,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M106" s="2" t="n"/>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N106" s="2" t="n"/>
-      <c r="O106" s="2" t="n"/>
-      <c r="P106" s="2" t="n"/>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>Nguelemendouka</t>
+        </is>
+      </c>
       <c r="Q106" s="2" t="n"/>
       <c r="R106" s="2" t="n"/>
       <c r="S106" s="2" t="n"/>
@@ -11409,10 +12633,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M107" s="2" t="n"/>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N107" s="2" t="n"/>
-      <c r="O107" s="2" t="n"/>
-      <c r="P107" s="2" t="n"/>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>Lomié</t>
+        </is>
+      </c>
       <c r="Q107" s="2" t="n"/>
       <c r="R107" s="2" t="n"/>
       <c r="S107" s="2" t="n"/>
@@ -11511,10 +12747,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M108" s="2" t="n"/>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N108" s="2" t="n"/>
-      <c r="O108" s="2" t="n"/>
-      <c r="P108" s="2" t="n"/>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>Doumé</t>
+        </is>
+      </c>
       <c r="Q108" s="2" t="n"/>
       <c r="R108" s="2" t="n"/>
       <c r="S108" s="2" t="n"/>
@@ -11613,10 +12861,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M109" s="3" t="n"/>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N109" s="3" t="n"/>
-      <c r="O109" s="3" t="n"/>
-      <c r="P109" s="3" t="n"/>
+      <c r="O109" s="3" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P109" s="3" t="inlineStr">
+        <is>
+          <t>Mouloundou</t>
+        </is>
+      </c>
       <c r="Q109" s="3" t="n"/>
       <c r="R109" s="3" t="n"/>
       <c r="S109" s="3" t="n"/>
@@ -11715,10 +12975,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M110" s="2" t="n"/>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N110" s="2" t="n"/>
-      <c r="O110" s="2" t="n"/>
-      <c r="P110" s="2" t="n"/>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>Salapoumbé</t>
+        </is>
+      </c>
       <c r="Q110" s="2" t="n"/>
       <c r="R110" s="2" t="n"/>
       <c r="S110" s="2" t="n"/>
@@ -11817,10 +13089,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M111" s="2" t="n"/>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N111" s="2" t="n"/>
-      <c r="O111" s="2" t="n"/>
-      <c r="P111" s="2" t="n"/>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>Mandjou</t>
+        </is>
+      </c>
       <c r="Q111" s="2" t="n"/>
       <c r="R111" s="2" t="n"/>
       <c r="S111" s="2" t="n"/>
@@ -12009,10 +13293,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M113" s="2" t="n"/>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N113" s="2" t="n"/>
-      <c r="O113" s="2" t="n"/>
-      <c r="P113" s="2" t="n"/>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>Gari-Gombo</t>
+        </is>
+      </c>
       <c r="Q113" s="2" t="n"/>
       <c r="R113" s="2" t="n"/>
       <c r="S113" s="2" t="n"/>
@@ -12111,10 +13407,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M114" s="2" t="n"/>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N114" s="2" t="n"/>
-      <c r="O114" s="2" t="n"/>
-      <c r="P114" s="2" t="n"/>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>Diang</t>
+        </is>
+      </c>
       <c r="Q114" s="2" t="n"/>
       <c r="R114" s="2" t="n"/>
       <c r="S114" s="2" t="n"/>
@@ -12303,10 +13611,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M116" s="2" t="n"/>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N116" s="2" t="n"/>
-      <c r="O116" s="2" t="n"/>
-      <c r="P116" s="2" t="n"/>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>Dimako</t>
+        </is>
+      </c>
       <c r="Q116" s="2" t="n"/>
       <c r="R116" s="2" t="n"/>
       <c r="S116" s="2" t="n"/>
@@ -12405,10 +13725,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M117" s="3" t="n"/>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N117" s="3" t="n"/>
-      <c r="O117" s="3" t="n"/>
-      <c r="P117" s="3" t="n"/>
+      <c r="O117" s="3" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P117" s="3" t="inlineStr">
+        <is>
+          <t>Messock</t>
+        </is>
+      </c>
       <c r="Q117" s="3" t="n"/>
       <c r="R117" s="3" t="n"/>
       <c r="S117" s="3" t="n"/>
@@ -12777,10 +14109,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M121" s="2" t="n"/>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N121" s="2" t="n"/>
-      <c r="O121" s="2" t="n"/>
-      <c r="P121" s="2" t="n"/>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="inlineStr">
+        <is>
+          <t>Mboma</t>
+        </is>
+      </c>
       <c r="Q121" s="2" t="n"/>
       <c r="R121" s="2" t="n"/>
       <c r="S121" s="2" t="n"/>
@@ -12879,10 +14223,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M122" s="2" t="n"/>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N122" s="2" t="n"/>
-      <c r="O122" s="2" t="n"/>
-      <c r="P122" s="2" t="n"/>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="inlineStr">
+        <is>
+          <t>Doumaintang</t>
+        </is>
+      </c>
       <c r="Q122" s="2" t="n"/>
       <c r="R122" s="2" t="n"/>
       <c r="S122" s="2" t="n"/>
@@ -13071,10 +14427,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M124" s="2" t="n"/>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N124" s="2" t="n"/>
-      <c r="O124" s="2" t="n"/>
-      <c r="P124" s="2" t="n"/>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>Somalomo</t>
+        </is>
+      </c>
       <c r="Q124" s="2" t="n"/>
       <c r="R124" s="2" t="n"/>
       <c r="S124" s="2" t="n"/>
@@ -13173,10 +14541,22 @@
           <t>EastCameroon</t>
         </is>
       </c>
-      <c r="M125" s="2" t="n"/>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N125" s="2" t="n"/>
-      <c r="O125" s="2" t="n"/>
-      <c r="P125" s="2" t="n"/>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>CM-ES</t>
+        </is>
+      </c>
+      <c r="P125" s="2" t="inlineStr">
+        <is>
+          <t>Ngoyla</t>
+        </is>
+      </c>
       <c r="Q125" s="2" t="n"/>
       <c r="R125" s="2" t="n"/>
       <c r="S125" s="2" t="n"/>
@@ -13281,10 +14661,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M126" s="2" t="n"/>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N126" s="2" t="n"/>
-      <c r="O126" s="2" t="n"/>
-      <c r="P126" s="2" t="n"/>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P126" s="2" t="inlineStr">
+        <is>
+          <t>Maroua I</t>
+        </is>
+      </c>
       <c r="Q126" s="2" t="n"/>
       <c r="R126" s="2" t="n"/>
       <c r="S126" s="2" t="n"/>
@@ -13389,10 +14781,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M127" s="2" t="n"/>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N127" s="2" t="n"/>
-      <c r="O127" s="2" t="n"/>
-      <c r="P127" s="2" t="n"/>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P127" s="2" t="inlineStr">
+        <is>
+          <t>Maroua II</t>
+        </is>
+      </c>
       <c r="Q127" s="2" t="n"/>
       <c r="R127" s="2" t="n"/>
       <c r="S127" s="2" t="n"/>
@@ -13497,10 +14901,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M128" s="2" t="n"/>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N128" s="2" t="n"/>
-      <c r="O128" s="2" t="n"/>
-      <c r="P128" s="2" t="n"/>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="inlineStr">
+        <is>
+          <t>Maroua III</t>
+        </is>
+      </c>
       <c r="Q128" s="2" t="n"/>
       <c r="R128" s="2" t="n"/>
       <c r="S128" s="2" t="n"/>
@@ -13599,10 +15015,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M129" s="2" t="n"/>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N129" s="2" t="n"/>
-      <c r="O129" s="2" t="n"/>
-      <c r="P129" s="2" t="n"/>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr">
+        <is>
+          <t>Mokolo</t>
+        </is>
+      </c>
       <c r="Q129" s="2" t="n"/>
       <c r="R129" s="2" t="n"/>
       <c r="S129" s="2" t="n"/>
@@ -13701,10 +15129,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M130" s="2" t="n"/>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N130" s="2" t="n"/>
-      <c r="O130" s="2" t="n"/>
-      <c r="P130" s="2" t="n"/>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
       <c r="Q130" s="2" t="n"/>
       <c r="R130" s="2" t="n"/>
       <c r="S130" s="2" t="n"/>
@@ -13803,10 +15243,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M131" s="2" t="n"/>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N131" s="2" t="n"/>
-      <c r="O131" s="2" t="n"/>
-      <c r="P131" s="2" t="n"/>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="inlineStr">
+        <is>
+          <t>Mogodé</t>
+        </is>
+      </c>
       <c r="Q131" s="2" t="n"/>
       <c r="R131" s="2" t="n"/>
       <c r="S131" s="2" t="n"/>
@@ -13905,10 +15357,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M132" s="2" t="n"/>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N132" s="2" t="n"/>
-      <c r="O132" s="2" t="n"/>
-      <c r="P132" s="2" t="n"/>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>Kaélé</t>
+        </is>
+      </c>
       <c r="Q132" s="2" t="n"/>
       <c r="R132" s="2" t="n"/>
       <c r="S132" s="2" t="n"/>
@@ -14007,10 +15471,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M133" s="2" t="n"/>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N133" s="2" t="n"/>
-      <c r="O133" s="2" t="n"/>
-      <c r="P133" s="2" t="n"/>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P133" s="2" t="inlineStr">
+        <is>
+          <t>Makary</t>
+        </is>
+      </c>
       <c r="Q133" s="2" t="n"/>
       <c r="R133" s="2" t="n"/>
       <c r="S133" s="2" t="n"/>
@@ -14109,10 +15585,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M134" s="2" t="n"/>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N134" s="2" t="n"/>
-      <c r="O134" s="2" t="n"/>
-      <c r="P134" s="2" t="n"/>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P134" s="2" t="inlineStr">
+        <is>
+          <t>Kousséri</t>
+        </is>
+      </c>
       <c r="Q134" s="2" t="n"/>
       <c r="R134" s="2" t="n"/>
       <c r="S134" s="2" t="n"/>
@@ -14211,10 +15699,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M135" s="2" t="n"/>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N135" s="2" t="n"/>
-      <c r="O135" s="2" t="n"/>
-      <c r="P135" s="2" t="n"/>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="inlineStr">
+        <is>
+          <t>Bogo</t>
+        </is>
+      </c>
       <c r="Q135" s="2" t="n"/>
       <c r="R135" s="2" t="n"/>
       <c r="S135" s="2" t="n"/>
@@ -14313,10 +15813,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M136" s="2" t="n"/>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N136" s="2" t="n"/>
-      <c r="O136" s="2" t="n"/>
-      <c r="P136" s="2" t="n"/>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P136" s="2" t="inlineStr">
+        <is>
+          <t>Yagoua</t>
+        </is>
+      </c>
       <c r="Q136" s="2" t="n"/>
       <c r="R136" s="2" t="n"/>
       <c r="S136" s="2" t="n"/>
@@ -14415,10 +15927,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M137" s="2" t="n"/>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N137" s="2" t="n"/>
-      <c r="O137" s="2" t="n"/>
-      <c r="P137" s="2" t="n"/>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P137" s="2" t="inlineStr">
+        <is>
+          <t>Tokombéré</t>
+        </is>
+      </c>
       <c r="Q137" s="2" t="n"/>
       <c r="R137" s="2" t="n"/>
       <c r="S137" s="2" t="n"/>
@@ -14517,10 +16041,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M138" s="3" t="n"/>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N138" s="3" t="n"/>
-      <c r="O138" s="3" t="n"/>
-      <c r="P138" s="3" t="n"/>
+      <c r="O138" s="3" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P138" s="3" t="inlineStr">
+        <is>
+          <t>Bourha</t>
+        </is>
+      </c>
       <c r="Q138" s="3" t="n"/>
       <c r="R138" s="3" t="n"/>
       <c r="S138" s="3" t="n"/>
@@ -14619,10 +16155,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M139" s="2" t="n"/>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N139" s="2" t="n"/>
-      <c r="O139" s="2" t="n"/>
-      <c r="P139" s="2" t="n"/>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P139" s="2" t="inlineStr">
+        <is>
+          <t>Meri</t>
+        </is>
+      </c>
       <c r="Q139" s="2" t="n"/>
       <c r="R139" s="2" t="n"/>
       <c r="S139" s="2" t="n"/>
@@ -14721,10 +16269,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M140" s="2" t="n"/>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N140" s="2" t="n"/>
-      <c r="O140" s="2" t="n"/>
-      <c r="P140" s="2" t="n"/>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P140" s="2" t="inlineStr">
+        <is>
+          <t>Maga</t>
+        </is>
+      </c>
       <c r="Q140" s="2" t="n"/>
       <c r="R140" s="2" t="n"/>
       <c r="S140" s="2" t="n"/>
@@ -14823,10 +16383,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M141" s="2" t="n"/>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N141" s="2" t="n"/>
-      <c r="O141" s="2" t="n"/>
-      <c r="P141" s="2" t="n"/>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P141" s="2" t="inlineStr">
+        <is>
+          <t>Moulvoudaye</t>
+        </is>
+      </c>
       <c r="Q141" s="2" t="n"/>
       <c r="R141" s="2" t="n"/>
       <c r="S141" s="2" t="n"/>
@@ -14925,10 +16497,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M142" s="2" t="n"/>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N142" s="2" t="n"/>
-      <c r="O142" s="2" t="n"/>
-      <c r="P142" s="2" t="n"/>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P142" s="2" t="inlineStr">
+        <is>
+          <t>Koza</t>
+        </is>
+      </c>
       <c r="Q142" s="2" t="n"/>
       <c r="R142" s="2" t="n"/>
       <c r="S142" s="2" t="n"/>
@@ -15027,10 +16611,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M143" s="2" t="n"/>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N143" s="2" t="n"/>
-      <c r="O143" s="2" t="n"/>
-      <c r="P143" s="2" t="n"/>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P143" s="2" t="inlineStr">
+        <is>
+          <t>Kolofata</t>
+        </is>
+      </c>
       <c r="Q143" s="2" t="n"/>
       <c r="R143" s="2" t="n"/>
       <c r="S143" s="2" t="n"/>
@@ -15219,10 +16815,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M145" s="2" t="n"/>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N145" s="2" t="n"/>
-      <c r="O145" s="2" t="n"/>
-      <c r="P145" s="2" t="n"/>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P145" s="2" t="inlineStr">
+        <is>
+          <t>Goulfey قولفي</t>
+        </is>
+      </c>
       <c r="Q145" s="2" t="n"/>
       <c r="R145" s="2" t="n"/>
       <c r="S145" s="2" t="n"/>
@@ -15321,10 +16929,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M146" s="2" t="n"/>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N146" s="2" t="n"/>
-      <c r="O146" s="2" t="n"/>
-      <c r="P146" s="2" t="n"/>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="inlineStr">
+        <is>
+          <t>Soulèdé-Roua</t>
+        </is>
+      </c>
       <c r="Q146" s="2" t="n"/>
       <c r="R146" s="2" t="n"/>
       <c r="S146" s="2" t="n"/>
@@ -15423,10 +17043,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M147" s="2" t="n"/>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N147" s="2" t="n"/>
-      <c r="O147" s="2" t="n"/>
-      <c r="P147" s="2" t="n"/>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P147" s="2" t="inlineStr">
+        <is>
+          <t>Kai-Kai</t>
+        </is>
+      </c>
       <c r="Q147" s="2" t="n"/>
       <c r="R147" s="2" t="n"/>
       <c r="S147" s="2" t="n"/>
@@ -15525,10 +17157,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M148" s="2" t="n"/>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N148" s="2" t="n"/>
-      <c r="O148" s="2" t="n"/>
-      <c r="P148" s="2" t="n"/>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="inlineStr">
+        <is>
+          <t>Gobo</t>
+        </is>
+      </c>
       <c r="Q148" s="2" t="n"/>
       <c r="R148" s="2" t="n"/>
       <c r="S148" s="2" t="n"/>
@@ -15627,10 +17271,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M149" s="2" t="n"/>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N149" s="2" t="n"/>
-      <c r="O149" s="2" t="n"/>
-      <c r="P149" s="2" t="n"/>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P149" s="2" t="inlineStr">
+        <is>
+          <t>Logone-Birni</t>
+        </is>
+      </c>
       <c r="Q149" s="2" t="n"/>
       <c r="R149" s="2" t="n"/>
       <c r="S149" s="2" t="n"/>
@@ -15729,10 +17385,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M150" s="2" t="n"/>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N150" s="2" t="n"/>
-      <c r="O150" s="2" t="n"/>
-      <c r="P150" s="2" t="n"/>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="inlineStr">
+        <is>
+          <t>Mindif</t>
+        </is>
+      </c>
       <c r="Q150" s="2" t="n"/>
       <c r="R150" s="2" t="n"/>
       <c r="S150" s="2" t="n"/>
@@ -15831,10 +17499,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M151" s="2" t="n"/>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N151" s="2" t="n"/>
-      <c r="O151" s="2" t="n"/>
-      <c r="P151" s="2" t="n"/>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P151" s="2" t="inlineStr">
+        <is>
+          <t>Blangoua</t>
+        </is>
+      </c>
       <c r="Q151" s="2" t="n"/>
       <c r="R151" s="2" t="n"/>
       <c r="S151" s="2" t="n"/>
@@ -15933,10 +17613,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M152" s="2" t="n"/>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N152" s="2" t="n"/>
-      <c r="O152" s="2" t="n"/>
-      <c r="P152" s="2" t="n"/>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="inlineStr">
+        <is>
+          <t>Hina</t>
+        </is>
+      </c>
       <c r="Q152" s="2" t="n"/>
       <c r="R152" s="2" t="n"/>
       <c r="S152" s="2" t="n"/>
@@ -16035,10 +17727,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M153" s="2" t="n"/>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N153" s="2" t="n"/>
-      <c r="O153" s="2" t="n"/>
-      <c r="P153" s="2" t="n"/>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P153" s="2" t="inlineStr">
+        <is>
+          <t>Guidiguis</t>
+        </is>
+      </c>
       <c r="Q153" s="2" t="n"/>
       <c r="R153" s="2" t="n"/>
       <c r="S153" s="2" t="n"/>
@@ -16227,10 +17931,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M155" s="2" t="n"/>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N155" s="2" t="n"/>
-      <c r="O155" s="2" t="n"/>
-      <c r="P155" s="2" t="n"/>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P155" s="2" t="inlineStr">
+        <is>
+          <t>Kar-Hay</t>
+        </is>
+      </c>
       <c r="Q155" s="2" t="n"/>
       <c r="R155" s="2" t="n"/>
       <c r="S155" s="2" t="n"/>
@@ -16419,10 +18135,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M157" s="2" t="n"/>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N157" s="2" t="n"/>
-      <c r="O157" s="2" t="n"/>
-      <c r="P157" s="2" t="n"/>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="inlineStr">
+        <is>
+          <t>Moutourwa</t>
+        </is>
+      </c>
       <c r="Q157" s="2" t="n"/>
       <c r="R157" s="2" t="n"/>
       <c r="S157" s="2" t="n"/>
@@ -16611,10 +18339,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M159" s="2" t="n"/>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N159" s="2" t="n"/>
-      <c r="O159" s="2" t="n"/>
-      <c r="P159" s="2" t="n"/>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P159" s="2" t="inlineStr">
+        <is>
+          <t>Guéré</t>
+        </is>
+      </c>
       <c r="Q159" s="2" t="n"/>
       <c r="R159" s="2" t="n"/>
       <c r="S159" s="2" t="n"/>
@@ -16713,10 +18453,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M160" s="2" t="n"/>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N160" s="2" t="n"/>
-      <c r="O160" s="2" t="n"/>
-      <c r="P160" s="2" t="n"/>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr">
+        <is>
+          <t>Pétté</t>
+        </is>
+      </c>
       <c r="Q160" s="2" t="n"/>
       <c r="R160" s="2" t="n"/>
       <c r="S160" s="2" t="n"/>
@@ -16815,10 +18567,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M161" s="2" t="n"/>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N161" s="2" t="n"/>
-      <c r="O161" s="2" t="n"/>
-      <c r="P161" s="2" t="n"/>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P161" s="2" t="inlineStr">
+        <is>
+          <t>Fotokol</t>
+        </is>
+      </c>
       <c r="Q161" s="2" t="n"/>
       <c r="R161" s="2" t="n"/>
       <c r="S161" s="2" t="n"/>
@@ -16917,10 +18681,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M162" s="2" t="n"/>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N162" s="2" t="n"/>
-      <c r="O162" s="2" t="n"/>
-      <c r="P162" s="2" t="n"/>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="inlineStr">
+        <is>
+          <t>Dargala</t>
+        </is>
+      </c>
       <c r="Q162" s="2" t="n"/>
       <c r="R162" s="2" t="n"/>
       <c r="S162" s="2" t="n"/>
@@ -17019,10 +18795,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M163" s="2" t="n"/>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N163" s="2" t="n"/>
-      <c r="O163" s="2" t="n"/>
-      <c r="P163" s="2" t="n"/>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P163" s="2" t="inlineStr">
+        <is>
+          <t>Ndoukoula</t>
+        </is>
+      </c>
       <c r="Q163" s="2" t="n"/>
       <c r="R163" s="2" t="n"/>
       <c r="S163" s="2" t="n"/>
@@ -17121,10 +18909,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M164" s="3" t="n"/>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N164" s="3" t="n"/>
-      <c r="O164" s="3" t="n"/>
-      <c r="P164" s="3" t="n"/>
+      <c r="O164" s="3" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P164" s="3" t="inlineStr">
+        <is>
+          <t>Tchatibali</t>
+        </is>
+      </c>
       <c r="Q164" s="3" t="n"/>
       <c r="R164" s="3" t="n"/>
       <c r="S164" s="3" t="n"/>
@@ -17223,10 +19023,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M165" s="2" t="n"/>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N165" s="2" t="n"/>
-      <c r="O165" s="2" t="n"/>
-      <c r="P165" s="2" t="n"/>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="inlineStr">
+        <is>
+          <t>Datchéka</t>
+        </is>
+      </c>
       <c r="Q165" s="2" t="n"/>
       <c r="R165" s="2" t="n"/>
       <c r="S165" s="2" t="n"/>
@@ -17325,10 +19137,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M166" s="2" t="n"/>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N166" s="2" t="n"/>
-      <c r="O166" s="2" t="n"/>
-      <c r="P166" s="2" t="n"/>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>Wina</t>
+        </is>
+      </c>
       <c r="Q166" s="2" t="n"/>
       <c r="R166" s="2" t="n"/>
       <c r="S166" s="2" t="n"/>
@@ -17427,10 +19251,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M167" s="2" t="n"/>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N167" s="2" t="n"/>
-      <c r="O167" s="2" t="n"/>
-      <c r="P167" s="2" t="n"/>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="inlineStr">
+        <is>
+          <t>Gazawa</t>
+        </is>
+      </c>
       <c r="Q167" s="2" t="n"/>
       <c r="R167" s="2" t="n"/>
       <c r="S167" s="2" t="n"/>
@@ -17529,10 +19365,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M168" s="2" t="n"/>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N168" s="2" t="n"/>
-      <c r="O168" s="2" t="n"/>
-      <c r="P168" s="2" t="n"/>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="inlineStr">
+        <is>
+          <t>Kalfou</t>
+        </is>
+      </c>
       <c r="Q168" s="2" t="n"/>
       <c r="R168" s="2" t="n"/>
       <c r="S168" s="2" t="n"/>
@@ -17631,10 +19479,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M169" s="2" t="n"/>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N169" s="2" t="n"/>
-      <c r="O169" s="2" t="n"/>
-      <c r="P169" s="2" t="n"/>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="inlineStr">
+        <is>
+          <t>Zina</t>
+        </is>
+      </c>
       <c r="Q169" s="2" t="n"/>
       <c r="R169" s="2" t="n"/>
       <c r="S169" s="2" t="n"/>
@@ -17733,10 +19593,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M170" s="2" t="n"/>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N170" s="2" t="n"/>
-      <c r="O170" s="2" t="n"/>
-      <c r="P170" s="2" t="n"/>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="inlineStr">
+        <is>
+          <t>Darak</t>
+        </is>
+      </c>
       <c r="Q170" s="2" t="n"/>
       <c r="R170" s="2" t="n"/>
       <c r="S170" s="2" t="n"/>
@@ -17835,10 +19707,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M171" s="5" t="n"/>
+      <c r="M171" s="5" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N171" s="5" t="n"/>
-      <c r="O171" s="5" t="n"/>
-      <c r="P171" s="5" t="n"/>
+      <c r="O171" s="5" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P171" s="5" t="inlineStr">
+        <is>
+          <t>Hilé - Alifa</t>
+        </is>
+      </c>
       <c r="Q171" s="5" t="n"/>
       <c r="R171" s="5" t="n"/>
       <c r="S171" s="5" t="n"/>
@@ -17937,10 +19821,22 @@
           <t>Far NorthCameroon</t>
         </is>
       </c>
-      <c r="M172" s="2" t="n"/>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N172" s="2" t="n"/>
-      <c r="O172" s="2" t="n"/>
-      <c r="P172" s="2" t="n"/>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>CM-EN</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="inlineStr">
+        <is>
+          <t>Waza</t>
+        </is>
+      </c>
       <c r="Q172" s="2" t="n"/>
       <c r="R172" s="2" t="n"/>
       <c r="S172" s="2" t="n"/>
@@ -18045,10 +19941,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M173" s="2" t="n"/>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N173" s="2" t="n"/>
-      <c r="O173" s="2" t="n"/>
-      <c r="P173" s="2" t="n"/>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P173" s="2" t="inlineStr">
+        <is>
+          <t>Douala III</t>
+        </is>
+      </c>
       <c r="Q173" s="2" t="n"/>
       <c r="R173" s="2" t="n"/>
       <c r="S173" s="2" t="n"/>
@@ -18153,10 +20061,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M174" s="2" t="n"/>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N174" s="2" t="n"/>
-      <c r="O174" s="2" t="n"/>
-      <c r="P174" s="2" t="n"/>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P174" s="2" t="inlineStr">
+        <is>
+          <t>Douala V</t>
+        </is>
+      </c>
       <c r="Q174" s="2" t="n"/>
       <c r="R174" s="2" t="n"/>
       <c r="S174" s="2" t="n"/>
@@ -18261,10 +20181,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M175" s="2" t="n"/>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N175" s="2" t="n"/>
-      <c r="O175" s="2" t="n"/>
-      <c r="P175" s="2" t="n"/>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P175" s="2" t="inlineStr">
+        <is>
+          <t>Douala II</t>
+        </is>
+      </c>
       <c r="Q175" s="2" t="n"/>
       <c r="R175" s="2" t="n"/>
       <c r="S175" s="2" t="n"/>
@@ -18369,10 +20301,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M176" s="2" t="n"/>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N176" s="2" t="n"/>
-      <c r="O176" s="2" t="n"/>
-      <c r="P176" s="2" t="n"/>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P176" s="2" t="inlineStr">
+        <is>
+          <t>Douala IV</t>
+        </is>
+      </c>
       <c r="Q176" s="2" t="n"/>
       <c r="R176" s="2" t="n"/>
       <c r="S176" s="2" t="n"/>
@@ -18477,10 +20421,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M177" s="2" t="n"/>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N177" s="2" t="n"/>
-      <c r="O177" s="2" t="n"/>
-      <c r="P177" s="2" t="n"/>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P177" s="2" t="inlineStr">
+        <is>
+          <t>Douala I</t>
+        </is>
+      </c>
       <c r="Q177" s="2" t="n"/>
       <c r="R177" s="2" t="n"/>
       <c r="S177" s="2" t="n"/>
@@ -18585,10 +20541,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M178" s="2" t="n"/>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N178" s="2" t="n"/>
-      <c r="O178" s="2" t="n"/>
-      <c r="P178" s="2" t="n"/>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P178" s="2" t="inlineStr">
+        <is>
+          <t>Douala VI</t>
+        </is>
+      </c>
       <c r="Q178" s="2" t="n"/>
       <c r="R178" s="2" t="n"/>
       <c r="S178" s="2" t="n"/>
@@ -18680,8 +20648,10 @@
         </is>
       </c>
       <c r="I179" s="2" t="n"/>
-      <c r="J179" s="2" t="e">
-        <v>#N/A</v>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>Édéa</t>
+        </is>
       </c>
       <c r="K179" s="2" t="n">
         <v>2005</v>
@@ -18691,10 +20661,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M179" s="2" t="n"/>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N179" s="2" t="n"/>
-      <c r="O179" s="2" t="n"/>
-      <c r="P179" s="2" t="n"/>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P179" s="2" t="inlineStr">
+        <is>
+          <t>Édéa II</t>
+        </is>
+      </c>
       <c r="Q179" s="2" t="n"/>
       <c r="R179" s="2" t="n"/>
       <c r="S179" s="2" t="n"/>
@@ -18799,10 +20781,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M180" s="2" t="n"/>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N180" s="2" t="n"/>
-      <c r="O180" s="2" t="n"/>
-      <c r="P180" s="2" t="n"/>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P180" s="2" t="inlineStr">
+        <is>
+          <t>Loum</t>
+        </is>
+      </c>
       <c r="Q180" s="2" t="n"/>
       <c r="R180" s="2" t="n"/>
       <c r="S180" s="2" t="n"/>
@@ -18907,10 +20901,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M181" s="2" t="n"/>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N181" s="2" t="n"/>
-      <c r="O181" s="2" t="n"/>
-      <c r="P181" s="2" t="n"/>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P181" s="2" t="inlineStr">
+        <is>
+          <t>Mélong</t>
+        </is>
+      </c>
       <c r="Q181" s="2" t="n"/>
       <c r="R181" s="2" t="n"/>
       <c r="S181" s="2" t="n"/>
@@ -19015,10 +21021,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M182" s="2" t="n"/>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N182" s="2" t="n"/>
-      <c r="O182" s="2" t="n"/>
-      <c r="P182" s="2" t="n"/>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P182" s="2" t="inlineStr">
+        <is>
+          <t>Nkongsamba I</t>
+        </is>
+      </c>
       <c r="Q182" s="2" t="n"/>
       <c r="R182" s="2" t="n"/>
       <c r="S182" s="2" t="n"/>
@@ -19123,10 +21141,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M183" s="2" t="n"/>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N183" s="2" t="n"/>
-      <c r="O183" s="2" t="n"/>
-      <c r="P183" s="2" t="n"/>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P183" s="2" t="inlineStr">
+        <is>
+          <t>Nkongsamba II</t>
+        </is>
+      </c>
       <c r="Q183" s="2" t="n"/>
       <c r="R183" s="2" t="n"/>
       <c r="S183" s="2" t="n"/>
@@ -19231,10 +21261,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M184" s="2" t="n"/>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N184" s="2" t="n"/>
-      <c r="O184" s="2" t="n"/>
-      <c r="P184" s="2" t="n"/>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P184" s="2" t="inlineStr">
+        <is>
+          <t>Nkongsamba III</t>
+        </is>
+      </c>
       <c r="Q184" s="2" t="n"/>
       <c r="R184" s="2" t="n"/>
       <c r="S184" s="2" t="n"/>
@@ -19333,10 +21375,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M185" s="2" t="n"/>
+      <c r="M185" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N185" s="2" t="n"/>
-      <c r="O185" s="2" t="n"/>
-      <c r="P185" s="2" t="n"/>
+      <c r="O185" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P185" s="2" t="inlineStr">
+        <is>
+          <t>Édéa I</t>
+        </is>
+      </c>
       <c r="Q185" s="2" t="n"/>
       <c r="R185" s="2" t="n"/>
       <c r="S185" s="2" t="n"/>
@@ -19435,10 +21489,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M186" s="2" t="n"/>
+      <c r="M186" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N186" s="2" t="n"/>
-      <c r="O186" s="2" t="n"/>
-      <c r="P186" s="2" t="n"/>
+      <c r="O186" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P186" s="2" t="inlineStr">
+        <is>
+          <t>Mbanga</t>
+        </is>
+      </c>
       <c r="Q186" s="2" t="n"/>
       <c r="R186" s="2" t="n"/>
       <c r="S186" s="2" t="n"/>
@@ -19537,10 +21603,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M187" s="2" t="n"/>
+      <c r="M187" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N187" s="2" t="n"/>
-      <c r="O187" s="2" t="n"/>
-      <c r="P187" s="2" t="n"/>
+      <c r="O187" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P187" s="2" t="inlineStr">
+        <is>
+          <t>Manjo</t>
+        </is>
+      </c>
       <c r="Q187" s="2" t="n"/>
       <c r="R187" s="2" t="n"/>
       <c r="S187" s="2" t="n"/>
@@ -19819,10 +21897,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M190" s="2" t="n"/>
+      <c r="M190" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N190" s="2" t="n"/>
-      <c r="O190" s="2" t="n"/>
-      <c r="P190" s="2" t="n"/>
+      <c r="O190" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P190" s="2" t="inlineStr">
+        <is>
+          <t>Nkondjock</t>
+        </is>
+      </c>
       <c r="Q190" s="2" t="n"/>
       <c r="R190" s="2" t="n"/>
       <c r="S190" s="2" t="n"/>
@@ -19921,10 +22011,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M191" s="2" t="n"/>
+      <c r="M191" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N191" s="2" t="n"/>
-      <c r="O191" s="2" t="n"/>
-      <c r="P191" s="2" t="n"/>
+      <c r="O191" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P191" s="2" t="inlineStr">
+        <is>
+          <t>Dibombari</t>
+        </is>
+      </c>
       <c r="Q191" s="2" t="n"/>
       <c r="R191" s="2" t="n"/>
       <c r="S191" s="2" t="n"/>
@@ -20023,10 +22125,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M192" s="2" t="n"/>
+      <c r="M192" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N192" s="2" t="n"/>
-      <c r="O192" s="2" t="n"/>
-      <c r="P192" s="2" t="n"/>
+      <c r="O192" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P192" s="2" t="inlineStr">
+        <is>
+          <t>Dizangué</t>
+        </is>
+      </c>
       <c r="Q192" s="2" t="n"/>
       <c r="R192" s="2" t="n"/>
       <c r="S192" s="2" t="n"/>
@@ -20305,10 +22419,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M195" s="2" t="n"/>
+      <c r="M195" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N195" s="2" t="n"/>
-      <c r="O195" s="2" t="n"/>
-      <c r="P195" s="2" t="n"/>
+      <c r="O195" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P195" s="2" t="inlineStr">
+        <is>
+          <t>Pouma</t>
+        </is>
+      </c>
       <c r="Q195" s="2" t="n"/>
       <c r="R195" s="2" t="n"/>
       <c r="S195" s="2" t="n"/>
@@ -20407,10 +22533,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M196" s="2" t="n"/>
+      <c r="M196" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N196" s="2" t="n"/>
-      <c r="O196" s="2" t="n"/>
-      <c r="P196" s="2" t="n"/>
+      <c r="O196" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P196" s="2" t="inlineStr">
+        <is>
+          <t>Yabassi</t>
+        </is>
+      </c>
       <c r="Q196" s="2" t="n"/>
       <c r="R196" s="2" t="n"/>
       <c r="S196" s="2" t="n"/>
@@ -20509,10 +22647,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M197" s="2" t="n"/>
+      <c r="M197" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N197" s="2" t="n"/>
-      <c r="O197" s="2" t="n"/>
-      <c r="P197" s="2" t="n"/>
+      <c r="O197" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P197" s="2" t="inlineStr">
+        <is>
+          <t>Nyanon</t>
+        </is>
+      </c>
       <c r="Q197" s="2" t="n"/>
       <c r="R197" s="2" t="n"/>
       <c r="S197" s="2" t="n"/>
@@ -20611,10 +22761,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M198" s="2" t="n"/>
+      <c r="M198" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N198" s="2" t="n"/>
-      <c r="O198" s="2" t="n"/>
-      <c r="P198" s="2" t="n"/>
+      <c r="O198" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P198" s="2" t="inlineStr">
+        <is>
+          <t>Ndom</t>
+        </is>
+      </c>
       <c r="Q198" s="2" t="n"/>
       <c r="R198" s="2" t="n"/>
       <c r="S198" s="2" t="n"/>
@@ -20713,10 +22875,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M199" s="2" t="n"/>
+      <c r="M199" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N199" s="2" t="n"/>
-      <c r="O199" s="2" t="n"/>
-      <c r="P199" s="2" t="n"/>
+      <c r="O199" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P199" s="2" t="inlineStr">
+        <is>
+          <t>Mouanko</t>
+        </is>
+      </c>
       <c r="Q199" s="2" t="n"/>
       <c r="R199" s="2" t="n"/>
       <c r="S199" s="2" t="n"/>
@@ -20815,10 +22989,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M200" s="2" t="n"/>
+      <c r="M200" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N200" s="2" t="n"/>
-      <c r="O200" s="2" t="n"/>
-      <c r="P200" s="2" t="n"/>
+      <c r="O200" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P200" s="2" t="inlineStr">
+        <is>
+          <t>Ngambé</t>
+        </is>
+      </c>
       <c r="Q200" s="2" t="n"/>
       <c r="R200" s="2" t="n"/>
       <c r="S200" s="2" t="n"/>
@@ -20917,10 +23103,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M201" s="2" t="n"/>
+      <c r="M201" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N201" s="2" t="n"/>
-      <c r="O201" s="2" t="n"/>
-      <c r="P201" s="2" t="n"/>
+      <c r="O201" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P201" s="2" t="inlineStr">
+        <is>
+          <t>Mombo</t>
+        </is>
+      </c>
       <c r="Q201" s="2" t="n"/>
       <c r="R201" s="2" t="n"/>
       <c r="S201" s="2" t="n"/>
@@ -21019,10 +23217,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M202" s="2" t="n"/>
+      <c r="M202" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N202" s="2" t="n"/>
-      <c r="O202" s="2" t="n"/>
-      <c r="P202" s="2" t="n"/>
+      <c r="O202" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P202" s="2" t="inlineStr">
+        <is>
+          <t>Dibamba</t>
+        </is>
+      </c>
       <c r="Q202" s="2" t="n"/>
       <c r="R202" s="2" t="n"/>
       <c r="S202" s="2" t="n"/>
@@ -21211,10 +23421,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M204" s="2" t="n"/>
+      <c r="M204" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N204" s="2" t="n"/>
-      <c r="O204" s="2" t="n"/>
-      <c r="P204" s="2" t="n"/>
+      <c r="O204" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P204" s="2" t="inlineStr">
+        <is>
+          <t>Ngwei</t>
+        </is>
+      </c>
       <c r="Q204" s="2" t="n"/>
       <c r="R204" s="2" t="n"/>
       <c r="S204" s="2" t="n"/>
@@ -21403,10 +23625,22 @@
           <t>LittoralCameroon</t>
         </is>
       </c>
-      <c r="M206" s="2" t="n"/>
+      <c r="M206" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N206" s="2" t="n"/>
-      <c r="O206" s="2" t="n"/>
-      <c r="P206" s="2" t="n"/>
+      <c r="O206" s="2" t="inlineStr">
+        <is>
+          <t>CM-LT</t>
+        </is>
+      </c>
+      <c r="P206" s="2" t="inlineStr">
+        <is>
+          <t>Yingui</t>
+        </is>
+      </c>
       <c r="Q206" s="2" t="n"/>
       <c r="R206" s="2" t="n"/>
       <c r="S206" s="2" t="n"/>
@@ -21511,10 +23745,22 @@
           <t>NorthCameroon</t>
         </is>
       </c>
-      <c r="M207" s="2" t="n"/>
+      <c r="M207" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N207" s="2" t="n"/>
-      <c r="O207" s="2" t="n"/>
-      <c r="P207" s="2" t="n"/>
+      <c r="O207" s="2" t="inlineStr">
+        <is>
+          <t>CM-NO</t>
+        </is>
+      </c>
+      <c r="P207" s="2" t="inlineStr">
+        <is>
+          <t>Garoua I</t>
+        </is>
+      </c>
       <c r="Q207" s="2" t="n"/>
       <c r="R207" s="2" t="n"/>
       <c r="S207" s="2" t="n"/>
@@ -21619,10 +23865,22 @@
           <t>NorthCameroon</t>
         </is>
       </c>
-      <c r="M208" s="2" t="n"/>
+      <c r="M208" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N208" s="2" t="n"/>
-      <c r="O208" s="2" t="n"/>
-      <c r="P208" s="2" t="n"/>
+      <c r="O208" s="2" t="inlineStr">
+        <is>
+          <t>CM-NO</t>
+        </is>
+      </c>
+      <c r="P208" s="2" t="inlineStr">
+        <is>
+          <t>Garoua II</t>
+        </is>
+      </c>
       <c r="Q208" s="2" t="n"/>
       <c r="R208" s="2" t="n"/>
       <c r="S208" s="2" t="n"/>
@@ -21727,10 +23985,22 @@
           <t>NorthCameroon</t>
         </is>
       </c>
-      <c r="M209" s="2" t="n"/>
+      <c r="M209" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N209" s="2" t="n"/>
-      <c r="O209" s="2" t="n"/>
-      <c r="P209" s="2" t="n"/>
+      <c r="O209" s="2" t="inlineStr">
+        <is>
+          <t>CM-NO</t>
+        </is>
+      </c>
+      <c r="P209" s="2" t="inlineStr">
+        <is>
+          <t>Garoua III</t>
+        </is>
+      </c>
       <c r="Q209" s="2" t="n"/>
       <c r="R209" s="2" t="n"/>
       <c r="S209" s="2" t="n"/>
@@ -21829,10 +24099,22 @@
           <t>NorthCameroon</t>
         </is>
       </c>
-      <c r="M210" s="2" t="n"/>
+      <c r="M210" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N210" s="2" t="n"/>
-      <c r="O210" s="2" t="n"/>
-      <c r="P210" s="2" t="n"/>
+      <c r="O210" s="2" t="inlineStr">
+        <is>
+          <t>CM-NO</t>
+        </is>
+      </c>
+      <c r="P210" s="2" t="inlineStr">
+        <is>
+          <t>Guider</t>
+        </is>
+      </c>
       <c r="Q210" s="2" t="n"/>
       <c r="R210" s="2" t="n"/>
       <c r="S210" s="2" t="n"/>
@@ -21931,10 +24213,22 @@
           <t>NorthCameroon</t>
         </is>
       </c>
-      <c r="M211" s="2" t="n"/>
+      <c r="M211" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N211" s="2" t="n"/>
-      <c r="O211" s="2" t="n"/>
-      <c r="P211" s="2" t="n"/>
+      <c r="O211" s="2" t="inlineStr">
+        <is>
+          <t>CM-NO</t>
+        </is>
+      </c>
+      <c r="P211" s="2" t="inlineStr">
+        <is>
+          <t>Touboro</t>
+        </is>
+      </c>
       <c r="Q211" s="2" t="n"/>
       <c r="R211" s="2" t="n"/>
       <c r="S211" s="2" t="n"/>
@@ -22033,10 +24327,22 @@
           <t>NorthCameroon</t>
         </is>
       </c>
-      <c r="M212" s="2" t="n"/>
+      <c r="M212" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N212" s="2" t="n"/>
-      <c r="O212" s="2" t="n"/>
-      <c r="P212" s="2" t="n"/>
+      <c r="O212" s="2" t="inlineStr">
+        <is>
+          <t>CM-NO</t>
+        </is>
+      </c>
+      <c r="P212" s="2" t="inlineStr">
+        <is>
+          <t>Lagdo</t>
+        </is>
+      </c>
       <c r="Q212" s="2" t="n"/>
       <c r="R212" s="2" t="n"/>
       <c r="S212" s="2" t="n"/>
@@ -22135,10 +24441,22 @@
           <t>NorthCameroon</t>
         </is>
       </c>
-      <c r="M213" s="2" t="n"/>
+      <c r="M213" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N213" s="2" t="n"/>
-      <c r="O213" s="2" t="n"/>
-      <c r="P213" s="2" t="n"/>
+      <c r="O213" s="2" t="inlineStr">
+        <is>
+          <t>CM-NO</t>
+        </is>
+      </c>
+      <c r="P213" s="2" t="inlineStr">
+        <is>
+          <t>Bibemi</t>
+        </is>
+      </c>
       <c r="Q213" s="2" t="n"/>
       <c r="R213" s="2" t="n"/>
       <c r="S213" s="2" t="n"/>
@@ -22237,10 +24555,22 @@
           <t>NorthCameroon</t>
         </is>
       </c>
-      <c r="M214" s="2" t="n"/>
+      <c r="M214" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N214" s="2" t="n"/>
-      <c r="O214" s="2" t="n"/>
-      <c r="P214" s="2" t="n"/>
+      <c r="O214" s="2" t="inlineStr">
+        <is>
+          <t>CM-NO</t>
+        </is>
+      </c>
+      <c r="P214" s="2" t="inlineStr">
+        <is>
+          <t>Rey-Bouba</t>
+        </is>
+      </c>
       <c r="Q214" s="2" t="n"/>
       <c r="R214" s="2" t="n"/>
       <c r="S214" s="2" t="n"/>
@@ -22339,10 +24669,22 @@
           <t>NorthCameroon</t>
         </is>
       </c>
-      <c r="M215" s="2" t="n"/>
+      <c r="M215" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N215" s="2" t="n"/>
-      <c r="O215" s="2" t="n"/>
-      <c r="P215" s="2" t="n"/>
+      <c r="O215" s="2" t="inlineStr">
+        <is>
+          <t>CM-NO</t>
+        </is>
+      </c>
+      <c r="P215" s="2" t="inlineStr">
+        <is>
+          <t>Mayo-Oulo</t>
+        </is>
+      </c>
       <c r="Q215" s="2" t="n"/>
       <c r="R215" s="2" t="n"/>
       <c r="S215" s="2" t="n"/>
@@ -22531,10 +24873,22 @@
           <t>NorthCameroon</t>
         </is>
       </c>
-      <c r="M217" s="2" t="n"/>
+      <c r="M217" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N217" s="2" t="n"/>
-      <c r="O217" s="2" t="n"/>
-      <c r="P217" s="2" t="n"/>
+      <c r="O217" s="2" t="inlineStr">
+        <is>
+          <t>CM-NO</t>
+        </is>
+      </c>
+      <c r="P217" s="2" t="inlineStr">
+        <is>
+          <t>Pitoa</t>
+        </is>
+      </c>
       <c r="Q217" s="2" t="n"/>
       <c r="R217" s="2" t="n"/>
       <c r="S217" s="2" t="n"/>
@@ -22633,10 +24987,22 @@
           <t>NorthCameroon</t>
         </is>
       </c>
-      <c r="M218" s="2" t="n"/>
+      <c r="M218" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N218" s="2" t="n"/>
-      <c r="O218" s="2" t="n"/>
-      <c r="P218" s="2" t="n"/>
+      <c r="O218" s="2" t="inlineStr">
+        <is>
+          <t>CM-NO</t>
+        </is>
+      </c>
+      <c r="P218" s="2" t="inlineStr">
+        <is>
+          <t>Figuil</t>
+        </is>
+      </c>
       <c r="Q218" s="2" t="n"/>
       <c r="R218" s="2" t="n"/>
       <c r="S218" s="2" t="n"/>
@@ -22735,10 +25101,22 @@
           <t>NorthCameroon</t>
         </is>
       </c>
-      <c r="M219" s="2" t="n"/>
+      <c r="M219" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N219" s="2" t="n"/>
-      <c r="O219" s="2" t="n"/>
-      <c r="P219" s="2" t="n"/>
+      <c r="O219" s="2" t="inlineStr">
+        <is>
+          <t>CM-NO</t>
+        </is>
+      </c>
+      <c r="P219" s="2" t="inlineStr">
+        <is>
+          <t>Madingring</t>
+        </is>
+      </c>
       <c r="Q219" s="2" t="n"/>
       <c r="R219" s="2" t="n"/>
       <c r="S219" s="2" t="n"/>
@@ -22837,10 +25215,22 @@
           <t>NorthCameroon</t>
         </is>
       </c>
-      <c r="M220" s="2" t="n"/>
+      <c r="M220" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N220" s="2" t="n"/>
-      <c r="O220" s="2" t="n"/>
-      <c r="P220" s="2" t="n"/>
+      <c r="O220" s="2" t="inlineStr">
+        <is>
+          <t>CM-NO</t>
+        </is>
+      </c>
+      <c r="P220" s="2" t="inlineStr">
+        <is>
+          <t>Tcholliré</t>
+        </is>
+      </c>
       <c r="Q220" s="2" t="n"/>
       <c r="R220" s="2" t="n"/>
       <c r="S220" s="2" t="n"/>
@@ -22939,10 +25329,22 @@
           <t>NorthCameroon</t>
         </is>
       </c>
-      <c r="M221" s="2" t="n"/>
+      <c r="M221" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N221" s="2" t="n"/>
-      <c r="O221" s="2" t="n"/>
-      <c r="P221" s="2" t="n"/>
+      <c r="O221" s="2" t="inlineStr">
+        <is>
+          <t>CM-NO</t>
+        </is>
+      </c>
+      <c r="P221" s="2" t="inlineStr">
+        <is>
+          <t>Touroua</t>
+        </is>
+      </c>
       <c r="Q221" s="2" t="n"/>
       <c r="R221" s="2" t="n"/>
       <c r="S221" s="2" t="n"/>
@@ -23041,10 +25443,22 @@
           <t>NorthCameroon</t>
         </is>
       </c>
-      <c r="M222" s="2" t="n"/>
+      <c r="M222" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N222" s="2" t="n"/>
-      <c r="O222" s="2" t="n"/>
-      <c r="P222" s="2" t="n"/>
+      <c r="O222" s="2" t="inlineStr">
+        <is>
+          <t>CM-NO</t>
+        </is>
+      </c>
+      <c r="P222" s="2" t="inlineStr">
+        <is>
+          <t>Poli</t>
+        </is>
+      </c>
       <c r="Q222" s="2" t="n"/>
       <c r="R222" s="2" t="n"/>
       <c r="S222" s="2" t="n"/>
@@ -23233,10 +25647,22 @@
           <t>NorthCameroon</t>
         </is>
       </c>
-      <c r="M224" s="2" t="n"/>
+      <c r="M224" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N224" s="2" t="n"/>
-      <c r="O224" s="2" t="n"/>
-      <c r="P224" s="2" t="n"/>
+      <c r="O224" s="2" t="inlineStr">
+        <is>
+          <t>CM-NO</t>
+        </is>
+      </c>
+      <c r="P224" s="2" t="inlineStr">
+        <is>
+          <t>Béka</t>
+        </is>
+      </c>
       <c r="Q224" s="2" t="n"/>
       <c r="R224" s="2" t="n"/>
       <c r="S224" s="2" t="n"/>
@@ -23335,10 +25761,22 @@
           <t>NorthCameroon</t>
         </is>
       </c>
-      <c r="M225" s="2" t="n"/>
+      <c r="M225" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N225" s="2" t="n"/>
-      <c r="O225" s="2" t="n"/>
-      <c r="P225" s="2" t="n"/>
+      <c r="O225" s="2" t="inlineStr">
+        <is>
+          <t>CM-NO</t>
+        </is>
+      </c>
+      <c r="P225" s="2" t="inlineStr">
+        <is>
+          <t>Baschéo</t>
+        </is>
+      </c>
       <c r="Q225" s="2" t="n"/>
       <c r="R225" s="2" t="n"/>
       <c r="S225" s="2" t="n"/>
@@ -23437,10 +25875,22 @@
           <t>NorthCameroon</t>
         </is>
       </c>
-      <c r="M226" s="2" t="n"/>
+      <c r="M226" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N226" s="2" t="n"/>
-      <c r="O226" s="2" t="n"/>
-      <c r="P226" s="2" t="n"/>
+      <c r="O226" s="2" t="inlineStr">
+        <is>
+          <t>CM-NO</t>
+        </is>
+      </c>
+      <c r="P226" s="2" t="inlineStr">
+        <is>
+          <t>Mayo-Hourna</t>
+        </is>
+      </c>
       <c r="Q226" s="2" t="n"/>
       <c r="R226" s="2" t="n"/>
       <c r="S226" s="2" t="n"/>
@@ -23539,10 +25989,22 @@
           <t>NorthCameroon</t>
         </is>
       </c>
-      <c r="M227" s="2" t="n"/>
+      <c r="M227" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N227" s="2" t="n"/>
-      <c r="O227" s="2" t="n"/>
-      <c r="P227" s="2" t="n"/>
+      <c r="O227" s="2" t="inlineStr">
+        <is>
+          <t>CM-NO</t>
+        </is>
+      </c>
+      <c r="P227" s="2" t="inlineStr">
+        <is>
+          <t>Dembo</t>
+        </is>
+      </c>
       <c r="Q227" s="2" t="n"/>
       <c r="R227" s="2" t="n"/>
       <c r="S227" s="2" t="n"/>
@@ -23647,10 +26109,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M228" s="3" t="n"/>
+      <c r="M228" s="3" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N228" s="3" t="n"/>
-      <c r="O228" s="3" t="n"/>
-      <c r="P228" s="3" t="n"/>
+      <c r="O228" s="3" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P228" s="3" t="inlineStr">
+        <is>
+          <t>Bamenda I</t>
+        </is>
+      </c>
       <c r="Q228" s="3" t="n"/>
       <c r="R228" s="3" t="n"/>
       <c r="S228" s="3" t="n"/>
@@ -23755,10 +26229,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M229" s="5" t="n"/>
+      <c r="M229" s="5" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N229" s="5" t="n"/>
-      <c r="O229" s="5" t="n"/>
-      <c r="P229" s="5" t="n"/>
+      <c r="O229" s="5" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P229" s="5" t="inlineStr">
+        <is>
+          <t>Bamenda I</t>
+        </is>
+      </c>
       <c r="Q229" s="5" t="n"/>
       <c r="R229" s="5" t="n"/>
       <c r="S229" s="5" t="n"/>
@@ -23863,10 +26349,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M230" s="2" t="n"/>
+      <c r="M230" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N230" s="2" t="n"/>
-      <c r="O230" s="2" t="n"/>
-      <c r="P230" s="2" t="n"/>
+      <c r="O230" s="2" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P230" s="2" t="inlineStr">
+        <is>
+          <t>Bamenda I</t>
+        </is>
+      </c>
       <c r="Q230" s="2" t="n"/>
       <c r="R230" s="2" t="n"/>
       <c r="S230" s="2" t="n"/>
@@ -24055,10 +26553,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M232" s="2" t="n"/>
+      <c r="M232" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N232" s="2" t="n"/>
-      <c r="O232" s="2" t="n"/>
-      <c r="P232" s="2" t="n"/>
+      <c r="O232" s="2" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P232" s="2" t="inlineStr">
+        <is>
+          <t>Kumbo</t>
+        </is>
+      </c>
       <c r="Q232" s="2" t="n"/>
       <c r="R232" s="2" t="n"/>
       <c r="S232" s="2" t="n"/>
@@ -24157,10 +26667,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M233" s="2" t="n"/>
+      <c r="M233" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N233" s="2" t="n"/>
-      <c r="O233" s="2" t="n"/>
-      <c r="P233" s="2" t="n"/>
+      <c r="O233" s="2" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P233" s="2" t="inlineStr">
+        <is>
+          <t>Ndu</t>
+        </is>
+      </c>
       <c r="Q233" s="2" t="n"/>
       <c r="R233" s="2" t="n"/>
       <c r="S233" s="2" t="n"/>
@@ -24259,10 +26781,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M234" s="2" t="n"/>
+      <c r="M234" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N234" s="2" t="n"/>
-      <c r="O234" s="2" t="n"/>
-      <c r="P234" s="2" t="n"/>
+      <c r="O234" s="2" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P234" s="2" t="inlineStr">
+        <is>
+          <t>Nwa</t>
+        </is>
+      </c>
       <c r="Q234" s="2" t="n"/>
       <c r="R234" s="2" t="n"/>
       <c r="S234" s="2" t="n"/>
@@ -24361,10 +26895,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M235" s="2" t="n"/>
+      <c r="M235" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N235" s="2" t="n"/>
-      <c r="O235" s="2" t="n"/>
-      <c r="P235" s="2" t="n"/>
+      <c r="O235" s="2" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P235" s="2" t="inlineStr">
+        <is>
+          <t>Ndop</t>
+        </is>
+      </c>
       <c r="Q235" s="2" t="n"/>
       <c r="R235" s="2" t="n"/>
       <c r="S235" s="2" t="n"/>
@@ -24463,10 +27009,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M236" s="2" t="n"/>
+      <c r="M236" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N236" s="2" t="n"/>
-      <c r="O236" s="2" t="n"/>
-      <c r="P236" s="2" t="n"/>
+      <c r="O236" s="2" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P236" s="2" t="inlineStr">
+        <is>
+          <t>Balikumbat</t>
+        </is>
+      </c>
       <c r="Q236" s="2" t="n"/>
       <c r="R236" s="2" t="n"/>
       <c r="S236" s="2" t="n"/>
@@ -24565,10 +27123,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M237" s="2" t="n"/>
+      <c r="M237" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N237" s="2" t="n"/>
-      <c r="O237" s="2" t="n"/>
-      <c r="P237" s="2" t="n"/>
+      <c r="O237" s="2" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P237" s="2" t="inlineStr">
+        <is>
+          <t>Santa</t>
+        </is>
+      </c>
       <c r="Q237" s="2" t="n"/>
       <c r="R237" s="2" t="n"/>
       <c r="S237" s="2" t="n"/>
@@ -24667,10 +27237,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M238" s="2" t="n"/>
+      <c r="M238" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N238" s="2" t="n"/>
-      <c r="O238" s="2" t="n"/>
-      <c r="P238" s="2" t="n"/>
+      <c r="O238" s="2" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P238" s="2" t="inlineStr">
+        <is>
+          <t>Nkambe</t>
+        </is>
+      </c>
       <c r="Q238" s="2" t="n"/>
       <c r="R238" s="2" t="n"/>
       <c r="S238" s="2" t="n"/>
@@ -24859,10 +27441,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M240" s="2" t="n"/>
+      <c r="M240" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N240" s="2" t="n"/>
-      <c r="O240" s="2" t="n"/>
-      <c r="P240" s="2" t="n"/>
+      <c r="O240" s="2" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P240" s="2" t="inlineStr">
+        <is>
+          <t>Bafut</t>
+        </is>
+      </c>
       <c r="Q240" s="2" t="n"/>
       <c r="R240" s="2" t="n"/>
       <c r="S240" s="2" t="n"/>
@@ -25051,10 +27645,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M242" s="2" t="n"/>
+      <c r="M242" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N242" s="2" t="n"/>
-      <c r="O242" s="2" t="n"/>
-      <c r="P242" s="2" t="n"/>
+      <c r="O242" s="2" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P242" s="2" t="inlineStr">
+        <is>
+          <t>Babessi</t>
+        </is>
+      </c>
       <c r="Q242" s="2" t="n"/>
       <c r="R242" s="2" t="n"/>
       <c r="S242" s="2" t="n"/>
@@ -25153,10 +27759,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M243" s="2" t="n"/>
+      <c r="M243" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N243" s="2" t="n"/>
-      <c r="O243" s="2" t="n"/>
-      <c r="P243" s="2" t="n"/>
+      <c r="O243" s="2" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P243" s="2" t="inlineStr">
+        <is>
+          <t>Tubah</t>
+        </is>
+      </c>
       <c r="Q243" s="2" t="n"/>
       <c r="R243" s="2" t="n"/>
       <c r="S243" s="2" t="n"/>
@@ -25255,10 +27873,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M244" s="2" t="n"/>
+      <c r="M244" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N244" s="2" t="n"/>
-      <c r="O244" s="2" t="n"/>
-      <c r="P244" s="2" t="n"/>
+      <c r="O244" s="2" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P244" s="2" t="inlineStr">
+        <is>
+          <t>Jakiri</t>
+        </is>
+      </c>
       <c r="Q244" s="2" t="n"/>
       <c r="R244" s="2" t="n"/>
       <c r="S244" s="2" t="n"/>
@@ -25357,10 +27987,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M245" s="2" t="n"/>
+      <c r="M245" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N245" s="2" t="n"/>
-      <c r="O245" s="2" t="n"/>
-      <c r="P245" s="2" t="n"/>
+      <c r="O245" s="2" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P245" s="2" t="inlineStr">
+        <is>
+          <t>Fundong</t>
+        </is>
+      </c>
       <c r="Q245" s="2" t="n"/>
       <c r="R245" s="2" t="n"/>
       <c r="S245" s="2" t="n"/>
@@ -25459,10 +28101,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M246" s="2" t="n"/>
+      <c r="M246" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N246" s="2" t="n"/>
-      <c r="O246" s="2" t="n"/>
-      <c r="P246" s="2" t="n"/>
+      <c r="O246" s="2" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P246" s="2" t="inlineStr">
+        <is>
+          <t>Batibo</t>
+        </is>
+      </c>
       <c r="Q246" s="2" t="n"/>
       <c r="R246" s="2" t="n"/>
       <c r="S246" s="2" t="n"/>
@@ -25561,10 +28215,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M247" s="2" t="n"/>
+      <c r="M247" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N247" s="2" t="n"/>
-      <c r="O247" s="2" t="n"/>
-      <c r="P247" s="2" t="n"/>
+      <c r="O247" s="2" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P247" s="2" t="inlineStr">
+        <is>
+          <t>Nkum</t>
+        </is>
+      </c>
       <c r="Q247" s="2" t="n"/>
       <c r="R247" s="2" t="n"/>
       <c r="S247" s="2" t="n"/>
@@ -25663,10 +28329,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M248" s="2" t="n"/>
+      <c r="M248" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N248" s="2" t="n"/>
-      <c r="O248" s="2" t="n"/>
-      <c r="P248" s="2" t="n"/>
+      <c r="O248" s="2" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P248" s="2" t="inlineStr">
+        <is>
+          <t>Belo</t>
+        </is>
+      </c>
       <c r="Q248" s="2" t="n"/>
       <c r="R248" s="2" t="n"/>
       <c r="S248" s="2" t="n"/>
@@ -25765,10 +28443,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M249" s="2" t="n"/>
+      <c r="M249" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N249" s="2" t="n"/>
-      <c r="O249" s="2" t="n"/>
-      <c r="P249" s="2" t="n"/>
+      <c r="O249" s="2" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P249" s="2" t="inlineStr">
+        <is>
+          <t>Ako</t>
+        </is>
+      </c>
       <c r="Q249" s="2" t="n"/>
       <c r="R249" s="2" t="n"/>
       <c r="S249" s="2" t="n"/>
@@ -25957,10 +28647,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M251" s="2" t="n"/>
+      <c r="M251" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N251" s="2" t="n"/>
-      <c r="O251" s="2" t="n"/>
-      <c r="P251" s="2" t="n"/>
+      <c r="O251" s="2" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P251" s="2" t="inlineStr">
+        <is>
+          <t>Wum</t>
+        </is>
+      </c>
       <c r="Q251" s="2" t="n"/>
       <c r="R251" s="2" t="n"/>
       <c r="S251" s="2" t="n"/>
@@ -26059,10 +28761,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M252" s="2" t="n"/>
+      <c r="M252" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N252" s="2" t="n"/>
-      <c r="O252" s="2" t="n"/>
-      <c r="P252" s="2" t="n"/>
+      <c r="O252" s="2" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P252" s="2" t="inlineStr">
+        <is>
+          <t>Mbengwi</t>
+        </is>
+      </c>
       <c r="Q252" s="2" t="n"/>
       <c r="R252" s="2" t="n"/>
       <c r="S252" s="2" t="n"/>
@@ -26161,10 +28875,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M253" s="2" t="n"/>
+      <c r="M253" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N253" s="2" t="n"/>
-      <c r="O253" s="2" t="n"/>
-      <c r="P253" s="2" t="n"/>
+      <c r="O253" s="2" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P253" s="2" t="inlineStr">
+        <is>
+          <t>Bali</t>
+        </is>
+      </c>
       <c r="Q253" s="2" t="n"/>
       <c r="R253" s="2" t="n"/>
       <c r="S253" s="2" t="n"/>
@@ -26353,10 +29079,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M255" s="2" t="n"/>
+      <c r="M255" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N255" s="2" t="n"/>
-      <c r="O255" s="2" t="n"/>
-      <c r="P255" s="2" t="n"/>
+      <c r="O255" s="2" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P255" s="2" t="inlineStr">
+        <is>
+          <t>Misaje</t>
+        </is>
+      </c>
       <c r="Q255" s="2" t="n"/>
       <c r="R255" s="2" t="n"/>
       <c r="S255" s="2" t="n"/>
@@ -26455,10 +29193,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M256" s="2" t="n"/>
+      <c r="M256" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N256" s="2" t="n"/>
-      <c r="O256" s="2" t="n"/>
-      <c r="P256" s="2" t="n"/>
+      <c r="O256" s="2" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P256" s="2" t="inlineStr">
+        <is>
+          <t>Njinikom</t>
+        </is>
+      </c>
       <c r="Q256" s="2" t="n"/>
       <c r="R256" s="2" t="n"/>
       <c r="S256" s="2" t="n"/>
@@ -26827,10 +29577,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M260" s="5" t="n"/>
+      <c r="M260" s="5" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N260" s="5" t="n"/>
-      <c r="O260" s="5" t="n"/>
-      <c r="P260" s="5" t="n"/>
+      <c r="O260" s="5" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P260" s="5" t="inlineStr">
+        <is>
+          <t>Nijkwa</t>
+        </is>
+      </c>
       <c r="Q260" s="5" t="n"/>
       <c r="R260" s="5" t="n"/>
       <c r="S260" s="5" t="n"/>
@@ -26929,10 +29691,22 @@
           <t>NorthwestCameroon</t>
         </is>
       </c>
-      <c r="M261" s="2" t="n"/>
+      <c r="M261" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N261" s="2" t="n"/>
-      <c r="O261" s="2" t="n"/>
-      <c r="P261" s="2" t="n"/>
+      <c r="O261" s="2" t="inlineStr">
+        <is>
+          <t>CM-NW</t>
+        </is>
+      </c>
+      <c r="P261" s="2" t="inlineStr">
+        <is>
+          <t>Furu-Awa</t>
+        </is>
+      </c>
       <c r="Q261" s="2" t="n"/>
       <c r="R261" s="2" t="n"/>
       <c r="S261" s="2" t="n"/>
@@ -27037,10 +29811,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M262" s="2" t="n"/>
+      <c r="M262" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N262" s="2" t="n"/>
-      <c r="O262" s="2" t="n"/>
-      <c r="P262" s="2" t="n"/>
+      <c r="O262" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P262" s="2" t="inlineStr">
+        <is>
+          <t>Sangmélima</t>
+        </is>
+      </c>
       <c r="Q262" s="2" t="n"/>
       <c r="R262" s="2" t="n"/>
       <c r="S262" s="2" t="n"/>
@@ -27139,10 +29925,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M263" s="2" t="n"/>
+      <c r="M263" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N263" s="2" t="n"/>
-      <c r="O263" s="2" t="n"/>
-      <c r="P263" s="2" t="n"/>
+      <c r="O263" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P263" s="2" t="inlineStr">
+        <is>
+          <t>Ebolowa II</t>
+        </is>
+      </c>
       <c r="Q263" s="2" t="n"/>
       <c r="R263" s="2" t="n"/>
       <c r="S263" s="2" t="n"/>
@@ -27241,10 +30039,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M264" s="2" t="n"/>
+      <c r="M264" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N264" s="2" t="n"/>
-      <c r="O264" s="2" t="n"/>
-      <c r="P264" s="2" t="n"/>
+      <c r="O264" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P264" s="2" t="inlineStr">
+        <is>
+          <t>Ambam</t>
+        </is>
+      </c>
       <c r="Q264" s="2" t="n"/>
       <c r="R264" s="2" t="n"/>
       <c r="S264" s="2" t="n"/>
@@ -27343,10 +30153,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M265" s="2" t="n"/>
+      <c r="M265" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N265" s="2" t="n"/>
-      <c r="O265" s="2" t="n"/>
-      <c r="P265" s="2" t="n"/>
+      <c r="O265" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P265" s="2" t="inlineStr">
+        <is>
+          <t>Kribi II</t>
+        </is>
+      </c>
       <c r="Q265" s="2" t="n"/>
       <c r="R265" s="2" t="n"/>
       <c r="S265" s="2" t="n"/>
@@ -27445,10 +30267,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M266" s="2" t="n"/>
+      <c r="M266" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N266" s="2" t="n"/>
-      <c r="O266" s="2" t="n"/>
-      <c r="P266" s="2" t="n"/>
+      <c r="O266" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P266" s="2" t="inlineStr">
+        <is>
+          <t>Ebolowa I</t>
+        </is>
+      </c>
       <c r="Q266" s="2" t="n"/>
       <c r="R266" s="2" t="n"/>
       <c r="S266" s="2" t="n"/>
@@ -27547,10 +30381,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M267" s="2" t="n"/>
+      <c r="M267" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N267" s="2" t="n"/>
-      <c r="O267" s="2" t="n"/>
-      <c r="P267" s="2" t="n"/>
+      <c r="O267" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P267" s="2" t="inlineStr">
+        <is>
+          <t>Meyomessala</t>
+        </is>
+      </c>
       <c r="Q267" s="2" t="n"/>
       <c r="R267" s="2" t="n"/>
       <c r="S267" s="2" t="n"/>
@@ -27649,10 +30495,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M268" s="2" t="n"/>
+      <c r="M268" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N268" s="2" t="n"/>
-      <c r="O268" s="2" t="n"/>
-      <c r="P268" s="2" t="n"/>
+      <c r="O268" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P268" s="2" t="inlineStr">
+        <is>
+          <t>Zoétélé</t>
+        </is>
+      </c>
       <c r="Q268" s="2" t="n"/>
       <c r="R268" s="2" t="n"/>
       <c r="S268" s="2" t="n"/>
@@ -27751,10 +30609,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M269" s="2" t="n"/>
+      <c r="M269" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N269" s="2" t="n"/>
-      <c r="O269" s="2" t="n"/>
-      <c r="P269" s="2" t="n"/>
+      <c r="O269" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P269" s="2" t="inlineStr">
+        <is>
+          <t>Kribi I</t>
+        </is>
+      </c>
       <c r="Q269" s="2" t="n"/>
       <c r="R269" s="2" t="n"/>
       <c r="S269" s="2" t="n"/>
@@ -27853,10 +30723,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M270" s="2" t="n"/>
+      <c r="M270" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N270" s="2" t="n"/>
-      <c r="O270" s="2" t="n"/>
-      <c r="P270" s="2" t="n"/>
+      <c r="O270" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P270" s="2" t="inlineStr">
+        <is>
+          <t>Niété</t>
+        </is>
+      </c>
       <c r="Q270" s="2" t="n"/>
       <c r="R270" s="2" t="n"/>
       <c r="S270" s="2" t="n"/>
@@ -27955,10 +30837,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M271" s="2" t="n"/>
+      <c r="M271" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N271" s="2" t="n"/>
-      <c r="O271" s="2" t="n"/>
-      <c r="P271" s="2" t="n"/>
+      <c r="O271" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P271" s="2" t="inlineStr">
+        <is>
+          <t>Lokoundjé</t>
+        </is>
+      </c>
       <c r="Q271" s="2" t="n"/>
       <c r="R271" s="2" t="n"/>
       <c r="S271" s="2" t="n"/>
@@ -28057,10 +30951,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M272" s="2" t="n"/>
+      <c r="M272" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N272" s="2" t="n"/>
-      <c r="O272" s="2" t="n"/>
-      <c r="P272" s="2" t="n"/>
+      <c r="O272" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P272" s="2" t="inlineStr">
+        <is>
+          <t>Djoum</t>
+        </is>
+      </c>
       <c r="Q272" s="2" t="n"/>
       <c r="R272" s="2" t="n"/>
       <c r="S272" s="2" t="n"/>
@@ -28159,10 +31065,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M273" s="2" t="n"/>
+      <c r="M273" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N273" s="2" t="n"/>
-      <c r="O273" s="2" t="n"/>
-      <c r="P273" s="2" t="n"/>
+      <c r="O273" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P273" s="2" t="inlineStr">
+        <is>
+          <t>Mvengue</t>
+        </is>
+      </c>
       <c r="Q273" s="2" t="n"/>
       <c r="R273" s="2" t="n"/>
       <c r="S273" s="2" t="n"/>
@@ -28261,10 +31179,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M274" s="2" t="n"/>
+      <c r="M274" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N274" s="2" t="n"/>
-      <c r="O274" s="2" t="n"/>
-      <c r="P274" s="2" t="n"/>
+      <c r="O274" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P274" s="2" t="inlineStr">
+        <is>
+          <t>Mengong</t>
+        </is>
+      </c>
       <c r="Q274" s="2" t="n"/>
       <c r="R274" s="2" t="n"/>
       <c r="S274" s="2" t="n"/>
@@ -28363,10 +31293,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M275" s="2" t="n"/>
+      <c r="M275" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N275" s="2" t="n"/>
-      <c r="O275" s="2" t="n"/>
-      <c r="P275" s="2" t="n"/>
+      <c r="O275" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P275" s="2" t="inlineStr">
+        <is>
+          <t>Kyé-Ossi</t>
+        </is>
+      </c>
       <c r="Q275" s="2" t="n"/>
       <c r="R275" s="2" t="n"/>
       <c r="S275" s="2" t="n"/>
@@ -28465,10 +31407,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M276" s="2" t="n"/>
+      <c r="M276" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N276" s="2" t="n"/>
-      <c r="O276" s="2" t="n"/>
-      <c r="P276" s="2" t="n"/>
+      <c r="O276" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P276" s="2" t="inlineStr">
+        <is>
+          <t>Mvangan</t>
+        </is>
+      </c>
       <c r="Q276" s="2" t="n"/>
       <c r="R276" s="2" t="n"/>
       <c r="S276" s="2" t="n"/>
@@ -28567,10 +31521,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M277" s="2" t="n"/>
+      <c r="M277" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N277" s="2" t="n"/>
-      <c r="O277" s="2" t="n"/>
-      <c r="P277" s="2" t="n"/>
+      <c r="O277" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P277" s="2" t="inlineStr">
+        <is>
+          <t>Ngoulémakong</t>
+        </is>
+      </c>
       <c r="Q277" s="2" t="n"/>
       <c r="R277" s="2" t="n"/>
       <c r="S277" s="2" t="n"/>
@@ -28669,10 +31635,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M278" s="2" t="n"/>
+      <c r="M278" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N278" s="2" t="n"/>
-      <c r="O278" s="2" t="n"/>
-      <c r="P278" s="2" t="n"/>
+      <c r="O278" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P278" s="2" t="inlineStr">
+        <is>
+          <t>Lolodorf</t>
+        </is>
+      </c>
       <c r="Q278" s="2" t="n"/>
       <c r="R278" s="2" t="n"/>
       <c r="S278" s="2" t="n"/>
@@ -28771,10 +31749,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M279" s="2" t="n"/>
+      <c r="M279" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N279" s="2" t="n"/>
-      <c r="O279" s="2" t="n"/>
-      <c r="P279" s="2" t="n"/>
+      <c r="O279" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P279" s="2" t="inlineStr">
+        <is>
+          <t>Bipindi</t>
+        </is>
+      </c>
       <c r="Q279" s="2" t="n"/>
       <c r="R279" s="2" t="n"/>
       <c r="S279" s="2" t="n"/>
@@ -28873,10 +31863,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M280" s="2" t="n"/>
+      <c r="M280" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N280" s="2" t="n"/>
-      <c r="O280" s="2" t="n"/>
-      <c r="P280" s="2" t="n"/>
+      <c r="O280" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P280" s="2" t="inlineStr">
+        <is>
+          <t>Biwong-Bané</t>
+        </is>
+      </c>
       <c r="Q280" s="2" t="n"/>
       <c r="R280" s="2" t="n"/>
       <c r="S280" s="2" t="n"/>
@@ -28975,10 +31977,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M281" s="2" t="n"/>
+      <c r="M281" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N281" s="2" t="n"/>
-      <c r="O281" s="2" t="n"/>
-      <c r="P281" s="2" t="n"/>
+      <c r="O281" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P281" s="2" t="inlineStr">
+        <is>
+          <t>Bengbis</t>
+        </is>
+      </c>
       <c r="Q281" s="2" t="n"/>
       <c r="R281" s="2" t="n"/>
       <c r="S281" s="2" t="n"/>
@@ -29077,10 +32091,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M282" s="2" t="n"/>
+      <c r="M282" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N282" s="2" t="n"/>
-      <c r="O282" s="2" t="n"/>
-      <c r="P282" s="2" t="n"/>
+      <c r="O282" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P282" s="2" t="inlineStr">
+        <is>
+          <t>Biwong-Bulu</t>
+        </is>
+      </c>
       <c r="Q282" s="2" t="n"/>
       <c r="R282" s="2" t="n"/>
       <c r="S282" s="2" t="n"/>
@@ -29179,10 +32205,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M283" s="2" t="n"/>
+      <c r="M283" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N283" s="2" t="n"/>
-      <c r="O283" s="2" t="n"/>
-      <c r="P283" s="2" t="n"/>
+      <c r="O283" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P283" s="2" t="inlineStr">
+        <is>
+          <t>Ma'an</t>
+        </is>
+      </c>
       <c r="Q283" s="2" t="n"/>
       <c r="R283" s="2" t="n"/>
       <c r="S283" s="2" t="n"/>
@@ -29281,10 +32319,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M284" s="2" t="n"/>
+      <c r="M284" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N284" s="2" t="n"/>
-      <c r="O284" s="2" t="n"/>
-      <c r="P284" s="2" t="n"/>
+      <c r="O284" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P284" s="2" t="inlineStr">
+        <is>
+          <t>Meyomessi</t>
+        </is>
+      </c>
       <c r="Q284" s="2" t="n"/>
       <c r="R284" s="2" t="n"/>
       <c r="S284" s="2" t="n"/>
@@ -29383,10 +32433,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M285" s="2" t="n"/>
+      <c r="M285" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N285" s="2" t="n"/>
-      <c r="O285" s="2" t="n"/>
-      <c r="P285" s="2" t="n"/>
+      <c r="O285" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P285" s="2" t="inlineStr">
+        <is>
+          <t>Efoulan</t>
+        </is>
+      </c>
       <c r="Q285" s="2" t="n"/>
       <c r="R285" s="2" t="n"/>
       <c r="S285" s="2" t="n"/>
@@ -29485,10 +32547,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M286" s="2" t="n"/>
+      <c r="M286" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N286" s="2" t="n"/>
-      <c r="O286" s="2" t="n"/>
-      <c r="P286" s="2" t="n"/>
+      <c r="O286" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P286" s="2" t="inlineStr">
+        <is>
+          <t>Akom II</t>
+        </is>
+      </c>
       <c r="Q286" s="2" t="n"/>
       <c r="R286" s="2" t="n"/>
       <c r="S286" s="2" t="n"/>
@@ -29587,10 +32661,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M287" s="2" t="n"/>
+      <c r="M287" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N287" s="2" t="n"/>
-      <c r="O287" s="2" t="n"/>
-      <c r="P287" s="2" t="n"/>
+      <c r="O287" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P287" s="2" t="inlineStr">
+        <is>
+          <t>Olamzé</t>
+        </is>
+      </c>
       <c r="Q287" s="2" t="n"/>
       <c r="R287" s="2" t="n"/>
       <c r="S287" s="2" t="n"/>
@@ -29689,10 +32775,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M288" s="2" t="n"/>
+      <c r="M288" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N288" s="2" t="n"/>
-      <c r="O288" s="2" t="n"/>
-      <c r="P288" s="2" t="n"/>
+      <c r="O288" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P288" s="2" t="inlineStr">
+        <is>
+          <t>Campo</t>
+        </is>
+      </c>
       <c r="Q288" s="2" t="n"/>
       <c r="R288" s="2" t="n"/>
       <c r="S288" s="2" t="n"/>
@@ -29791,10 +32889,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M289" s="2" t="n"/>
+      <c r="M289" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N289" s="2" t="n"/>
-      <c r="O289" s="2" t="n"/>
-      <c r="P289" s="2" t="n"/>
+      <c r="O289" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P289" s="2" t="inlineStr">
+        <is>
+          <t>Mintom</t>
+        </is>
+      </c>
       <c r="Q289" s="2" t="n"/>
       <c r="R289" s="2" t="n"/>
       <c r="S289" s="2" t="n"/>
@@ -29893,10 +33003,22 @@
           <t>SouthCameroon</t>
         </is>
       </c>
-      <c r="M290" s="2" t="n"/>
+      <c r="M290" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N290" s="2" t="n"/>
-      <c r="O290" s="2" t="n"/>
-      <c r="P290" s="2" t="n"/>
+      <c r="O290" s="2" t="inlineStr">
+        <is>
+          <t>CM-SU</t>
+        </is>
+      </c>
+      <c r="P290" s="2" t="inlineStr">
+        <is>
+          <t>Oveng</t>
+        </is>
+      </c>
       <c r="Q290" s="2" t="n"/>
       <c r="R290" s="2" t="n"/>
       <c r="S290" s="2" t="n"/>
@@ -30001,10 +33123,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M291" s="2" t="n"/>
+      <c r="M291" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N291" s="2" t="n"/>
-      <c r="O291" s="2" t="n"/>
-      <c r="P291" s="2" t="n"/>
+      <c r="O291" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P291" s="2" t="inlineStr">
+        <is>
+          <t>Buea</t>
+        </is>
+      </c>
       <c r="Q291" s="2" t="n"/>
       <c r="R291" s="2" t="n"/>
       <c r="S291" s="2" t="n"/>
@@ -30109,10 +33243,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M292" s="2" t="n"/>
+      <c r="M292" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N292" s="2" t="n"/>
-      <c r="O292" s="2" t="n"/>
-      <c r="P292" s="2" t="n"/>
+      <c r="O292" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P292" s="2" t="inlineStr">
+        <is>
+          <t>Tiko</t>
+        </is>
+      </c>
       <c r="Q292" s="2" t="n"/>
       <c r="R292" s="2" t="n"/>
       <c r="S292" s="2" t="n"/>
@@ -30217,10 +33363,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M293" s="2" t="n"/>
+      <c r="M293" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N293" s="2" t="n"/>
-      <c r="O293" s="2" t="n"/>
-      <c r="P293" s="2" t="n"/>
+      <c r="O293" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P293" s="2" t="inlineStr">
+        <is>
+          <t>Limbé I</t>
+        </is>
+      </c>
       <c r="Q293" s="2" t="n"/>
       <c r="R293" s="2" t="n"/>
       <c r="S293" s="2" t="n"/>
@@ -30325,10 +33483,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M294" s="2" t="n"/>
+      <c r="M294" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N294" s="2" t="n"/>
-      <c r="O294" s="2" t="n"/>
-      <c r="P294" s="2" t="n"/>
+      <c r="O294" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P294" s="2" t="inlineStr">
+        <is>
+          <t>Muyuka</t>
+        </is>
+      </c>
       <c r="Q294" s="2" t="n"/>
       <c r="R294" s="2" t="n"/>
       <c r="S294" s="2" t="n"/>
@@ -30433,10 +33603,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M295" s="2" t="n"/>
+      <c r="M295" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N295" s="2" t="n"/>
-      <c r="O295" s="2" t="n"/>
-      <c r="P295" s="2" t="n"/>
+      <c r="O295" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P295" s="2" t="inlineStr">
+        <is>
+          <t>Limbé II</t>
+        </is>
+      </c>
       <c r="Q295" s="2" t="n"/>
       <c r="R295" s="2" t="n"/>
       <c r="S295" s="2" t="n"/>
@@ -30541,10 +33723,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M296" s="4" t="n"/>
+      <c r="M296" s="4" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N296" s="4" t="n"/>
-      <c r="O296" s="4" t="n"/>
-      <c r="P296" s="4" t="n"/>
+      <c r="O296" s="4" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P296" s="4" t="inlineStr">
+        <is>
+          <t>Idenau</t>
+        </is>
+      </c>
       <c r="Q296" s="4" t="n"/>
       <c r="R296" s="4" t="n"/>
       <c r="S296" s="4" t="n"/>
@@ -30637,10 +33831,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M297" s="2" t="n"/>
+      <c r="M297" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N297" s="2" t="n"/>
-      <c r="O297" s="2" t="n"/>
-      <c r="P297" s="2" t="n"/>
+      <c r="O297" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P297" s="2" t="inlineStr">
+        <is>
+          <t>Limbé III</t>
+        </is>
+      </c>
       <c r="Q297" s="2" t="n"/>
       <c r="R297" s="2" t="n"/>
       <c r="S297" s="2" t="n"/>
@@ -30739,10 +33945,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M298" s="2" t="n"/>
+      <c r="M298" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N298" s="2" t="n"/>
-      <c r="O298" s="2" t="n"/>
-      <c r="P298" s="2" t="n"/>
+      <c r="O298" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P298" s="2" t="inlineStr">
+        <is>
+          <t>Mbonge</t>
+        </is>
+      </c>
       <c r="Q298" s="2" t="n"/>
       <c r="R298" s="2" t="n"/>
       <c r="S298" s="2" t="n"/>
@@ -30841,10 +34059,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M299" s="2" t="n"/>
+      <c r="M299" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N299" s="2" t="n"/>
-      <c r="O299" s="2" t="n"/>
-      <c r="P299" s="2" t="n"/>
+      <c r="O299" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P299" s="2" t="inlineStr">
+        <is>
+          <t>Akwaya</t>
+        </is>
+      </c>
       <c r="Q299" s="2" t="n"/>
       <c r="R299" s="2" t="n"/>
       <c r="S299" s="2" t="n"/>
@@ -30943,10 +34173,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M300" s="2" t="n"/>
+      <c r="M300" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N300" s="2" t="n"/>
-      <c r="O300" s="2" t="n"/>
-      <c r="P300" s="2" t="n"/>
+      <c r="O300" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P300" s="2" t="inlineStr">
+        <is>
+          <t>Kumba I</t>
+        </is>
+      </c>
       <c r="Q300" s="2" t="n"/>
       <c r="R300" s="2" t="n"/>
       <c r="S300" s="2" t="n"/>
@@ -31045,10 +34287,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M301" s="2" t="n"/>
+      <c r="M301" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N301" s="2" t="n"/>
-      <c r="O301" s="2" t="n"/>
-      <c r="P301" s="2" t="n"/>
+      <c r="O301" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P301" s="2" t="inlineStr">
+        <is>
+          <t>Kumba II</t>
+        </is>
+      </c>
       <c r="Q301" s="2" t="n"/>
       <c r="R301" s="2" t="n"/>
       <c r="S301" s="2" t="n"/>
@@ -31147,10 +34401,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M302" s="2" t="n"/>
+      <c r="M302" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N302" s="2" t="n"/>
-      <c r="O302" s="2" t="n"/>
-      <c r="P302" s="2" t="n"/>
+      <c r="O302" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P302" s="2" t="inlineStr">
+        <is>
+          <t>Tombel</t>
+        </is>
+      </c>
       <c r="Q302" s="2" t="n"/>
       <c r="R302" s="2" t="n"/>
       <c r="S302" s="2" t="n"/>
@@ -31249,10 +34515,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M303" s="2" t="n"/>
+      <c r="M303" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N303" s="2" t="n"/>
-      <c r="O303" s="2" t="n"/>
-      <c r="P303" s="2" t="n"/>
+      <c r="O303" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P303" s="2" t="inlineStr">
+        <is>
+          <t>Ekondo-Titi</t>
+        </is>
+      </c>
       <c r="Q303" s="2" t="n"/>
       <c r="R303" s="2" t="n"/>
       <c r="S303" s="2" t="n"/>
@@ -31351,10 +34629,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M304" s="2" t="n"/>
+      <c r="M304" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N304" s="2" t="n"/>
-      <c r="O304" s="2" t="n"/>
-      <c r="P304" s="2" t="n"/>
+      <c r="O304" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P304" s="2" t="inlineStr">
+        <is>
+          <t>Konye</t>
+        </is>
+      </c>
       <c r="Q304" s="2" t="n"/>
       <c r="R304" s="2" t="n"/>
       <c r="S304" s="2" t="n"/>
@@ -31543,10 +34833,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M306" s="2" t="n"/>
+      <c r="M306" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N306" s="2" t="n"/>
-      <c r="O306" s="2" t="n"/>
-      <c r="P306" s="2" t="n"/>
+      <c r="O306" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P306" s="2" t="inlineStr">
+        <is>
+          <t>Wabane</t>
+        </is>
+      </c>
       <c r="Q306" s="2" t="n"/>
       <c r="R306" s="2" t="n"/>
       <c r="S306" s="2" t="n"/>
@@ -31645,10 +34947,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M307" s="2" t="n"/>
+      <c r="M307" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N307" s="2" t="n"/>
-      <c r="O307" s="2" t="n"/>
-      <c r="P307" s="2" t="n"/>
+      <c r="O307" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P307" s="2" t="inlineStr">
+        <is>
+          <t>Eyumodjock</t>
+        </is>
+      </c>
       <c r="Q307" s="2" t="n"/>
       <c r="R307" s="2" t="n"/>
       <c r="S307" s="2" t="n"/>
@@ -31747,10 +35061,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M308" s="2" t="n"/>
+      <c r="M308" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N308" s="2" t="n"/>
-      <c r="O308" s="2" t="n"/>
-      <c r="P308" s="2" t="n"/>
+      <c r="O308" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P308" s="2" t="inlineStr">
+        <is>
+          <t>Alou</t>
+        </is>
+      </c>
       <c r="Q308" s="2" t="n"/>
       <c r="R308" s="2" t="n"/>
       <c r="S308" s="2" t="n"/>
@@ -31849,10 +35175,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M309" s="2" t="n"/>
+      <c r="M309" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N309" s="2" t="n"/>
-      <c r="O309" s="2" t="n"/>
-      <c r="P309" s="2" t="n"/>
+      <c r="O309" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P309" s="2" t="inlineStr">
+        <is>
+          <t>Kumba III</t>
+        </is>
+      </c>
       <c r="Q309" s="2" t="n"/>
       <c r="R309" s="2" t="n"/>
       <c r="S309" s="2" t="n"/>
@@ -32131,10 +35469,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M312" s="2" t="n"/>
+      <c r="M312" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N312" s="2" t="n"/>
-      <c r="O312" s="2" t="n"/>
-      <c r="P312" s="2" t="n"/>
+      <c r="O312" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P312" s="2" t="inlineStr">
+        <is>
+          <t>Nguti</t>
+        </is>
+      </c>
       <c r="Q312" s="2" t="n"/>
       <c r="R312" s="2" t="n"/>
       <c r="S312" s="2" t="n"/>
@@ -32233,10 +35583,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M313" s="2" t="n"/>
+      <c r="M313" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N313" s="2" t="n"/>
-      <c r="O313" s="2" t="n"/>
-      <c r="P313" s="2" t="n"/>
+      <c r="O313" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P313" s="2" t="inlineStr">
+        <is>
+          <t>Bangem</t>
+        </is>
+      </c>
       <c r="Q313" s="2" t="n"/>
       <c r="R313" s="2" t="n"/>
       <c r="S313" s="2" t="n"/>
@@ -32335,10 +35697,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M314" s="2" t="n"/>
+      <c r="M314" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N314" s="2" t="n"/>
-      <c r="O314" s="2" t="n"/>
-      <c r="P314" s="2" t="n"/>
+      <c r="O314" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P314" s="2" t="inlineStr">
+        <is>
+          <t>Bamusso</t>
+        </is>
+      </c>
       <c r="Q314" s="2" t="n"/>
       <c r="R314" s="2" t="n"/>
       <c r="S314" s="2" t="n"/>
@@ -32437,10 +35811,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M315" s="3" t="n"/>
+      <c r="M315" s="3" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N315" s="3" t="n"/>
-      <c r="O315" s="3" t="n"/>
-      <c r="P315" s="3" t="n"/>
+      <c r="O315" s="3" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P315" s="3" t="inlineStr">
+        <is>
+          <t>Mudemba</t>
+        </is>
+      </c>
       <c r="Q315" s="3" t="n"/>
       <c r="R315" s="3" t="n"/>
       <c r="S315" s="3" t="n"/>
@@ -32539,10 +35925,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M316" s="2" t="n"/>
+      <c r="M316" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N316" s="2" t="n"/>
-      <c r="O316" s="2" t="n"/>
-      <c r="P316" s="2" t="n"/>
+      <c r="O316" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P316" s="2" t="inlineStr">
+        <is>
+          <t>Dikome-Balue</t>
+        </is>
+      </c>
       <c r="Q316" s="2" t="n"/>
       <c r="R316" s="2" t="n"/>
       <c r="S316" s="2" t="n"/>
@@ -32641,10 +36039,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M317" s="2" t="n"/>
+      <c r="M317" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N317" s="2" t="n"/>
-      <c r="O317" s="2" t="n"/>
-      <c r="P317" s="2" t="n"/>
+      <c r="O317" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P317" s="2" t="inlineStr">
+        <is>
+          <t>Toko</t>
+        </is>
+      </c>
       <c r="Q317" s="2" t="n"/>
       <c r="R317" s="2" t="n"/>
       <c r="S317" s="2" t="n"/>
@@ -32743,10 +36153,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M318" s="2" t="n"/>
+      <c r="M318" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N318" s="2" t="n"/>
-      <c r="O318" s="2" t="n"/>
-      <c r="P318" s="2" t="n"/>
+      <c r="O318" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P318" s="2" t="inlineStr">
+        <is>
+          <t>Idabato</t>
+        </is>
+      </c>
       <c r="Q318" s="2" t="n"/>
       <c r="R318" s="2" t="n"/>
       <c r="S318" s="2" t="n"/>
@@ -32845,10 +36267,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M319" s="2" t="n"/>
+      <c r="M319" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N319" s="2" t="n"/>
-      <c r="O319" s="2" t="n"/>
-      <c r="P319" s="2" t="n"/>
+      <c r="O319" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P319" s="2" t="inlineStr">
+        <is>
+          <t>Isanguele</t>
+        </is>
+      </c>
       <c r="Q319" s="2" t="n"/>
       <c r="R319" s="2" t="n"/>
       <c r="S319" s="2" t="n"/>
@@ -32947,10 +36381,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M320" s="2" t="n"/>
+      <c r="M320" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N320" s="2" t="n"/>
-      <c r="O320" s="2" t="n"/>
-      <c r="P320" s="2" t="n"/>
+      <c r="O320" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P320" s="2" t="inlineStr">
+        <is>
+          <t>Kombo-Itindi</t>
+        </is>
+      </c>
       <c r="Q320" s="2" t="n"/>
       <c r="R320" s="2" t="n"/>
       <c r="S320" s="2" t="n"/>
@@ -33049,10 +36495,22 @@
           <t>SouthwestCameroon</t>
         </is>
       </c>
-      <c r="M321" s="2" t="n"/>
+      <c r="M321" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N321" s="2" t="n"/>
-      <c r="O321" s="2" t="n"/>
-      <c r="P321" s="2" t="n"/>
+      <c r="O321" s="2" t="inlineStr">
+        <is>
+          <t>CM-SW</t>
+        </is>
+      </c>
+      <c r="P321" s="2" t="inlineStr">
+        <is>
+          <t>Kombo-Abedimo</t>
+        </is>
+      </c>
       <c r="Q321" s="2" t="n"/>
       <c r="R321" s="2" t="n"/>
       <c r="S321" s="2" t="n"/>
@@ -33157,10 +36615,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M322" s="2" t="n"/>
+      <c r="M322" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N322" s="2" t="n"/>
-      <c r="O322" s="2" t="n"/>
-      <c r="P322" s="2" t="n"/>
+      <c r="O322" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P322" s="2" t="inlineStr">
+        <is>
+          <t>Bafang</t>
+        </is>
+      </c>
       <c r="Q322" s="2" t="n"/>
       <c r="R322" s="2" t="n"/>
       <c r="S322" s="2" t="n"/>
@@ -33265,10 +36735,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M323" s="2" t="n"/>
+      <c r="M323" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N323" s="2" t="n"/>
-      <c r="O323" s="2" t="n"/>
-      <c r="P323" s="2" t="n"/>
+      <c r="O323" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P323" s="2" t="inlineStr">
+        <is>
+          <t>Bafoussam II</t>
+        </is>
+      </c>
       <c r="Q323" s="2" t="n"/>
       <c r="R323" s="2" t="n"/>
       <c r="S323" s="2" t="n"/>
@@ -33373,10 +36855,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M324" s="2" t="n"/>
+      <c r="M324" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N324" s="2" t="n"/>
-      <c r="O324" s="2" t="n"/>
-      <c r="P324" s="2" t="n"/>
+      <c r="O324" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P324" s="2" t="inlineStr">
+        <is>
+          <t>Bafoussam I</t>
+        </is>
+      </c>
       <c r="Q324" s="2" t="n"/>
       <c r="R324" s="2" t="n"/>
       <c r="S324" s="2" t="n"/>
@@ -33481,10 +36975,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M325" s="2" t="n"/>
+      <c r="M325" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N325" s="2" t="n"/>
-      <c r="O325" s="2" t="n"/>
-      <c r="P325" s="2" t="n"/>
+      <c r="O325" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P325" s="2" t="inlineStr">
+        <is>
+          <t>Bafoussam III</t>
+        </is>
+      </c>
       <c r="Q325" s="2" t="n"/>
       <c r="R325" s="2" t="n"/>
       <c r="S325" s="2" t="n"/>
@@ -33589,10 +37095,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M326" s="2" t="n"/>
+      <c r="M326" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N326" s="2" t="n"/>
-      <c r="O326" s="2" t="n"/>
-      <c r="P326" s="2" t="n"/>
+      <c r="O326" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P326" s="2" t="inlineStr">
+        <is>
+          <t>Bangangté</t>
+        </is>
+      </c>
       <c r="Q326" s="2" t="n"/>
       <c r="R326" s="2" t="n"/>
       <c r="S326" s="2" t="n"/>
@@ -33697,10 +37215,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M327" s="2" t="n"/>
+      <c r="M327" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N327" s="2" t="n"/>
-      <c r="O327" s="2" t="n"/>
-      <c r="P327" s="2" t="n"/>
+      <c r="O327" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P327" s="2" t="inlineStr">
+        <is>
+          <t>Dschang</t>
+        </is>
+      </c>
       <c r="Q327" s="2" t="n"/>
       <c r="R327" s="2" t="n"/>
       <c r="S327" s="2" t="n"/>
@@ -33805,10 +37335,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M328" s="2" t="n"/>
+      <c r="M328" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N328" s="2" t="n"/>
-      <c r="O328" s="2" t="n"/>
-      <c r="P328" s="2" t="n"/>
+      <c r="O328" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P328" s="2" t="inlineStr">
+        <is>
+          <t>Mbouda</t>
+        </is>
+      </c>
       <c r="Q328" s="2" t="n"/>
       <c r="R328" s="2" t="n"/>
       <c r="S328" s="2" t="n"/>
@@ -33907,10 +37449,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M329" s="2" t="n"/>
+      <c r="M329" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N329" s="2" t="n"/>
-      <c r="O329" s="2" t="n"/>
-      <c r="P329" s="2" t="n"/>
+      <c r="O329" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P329" s="2" t="inlineStr">
+        <is>
+          <t>Foumban</t>
+        </is>
+      </c>
       <c r="Q329" s="2" t="n"/>
       <c r="R329" s="2" t="n"/>
       <c r="S329" s="2" t="n"/>
@@ -34009,10 +37563,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M330" s="2" t="n"/>
+      <c r="M330" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N330" s="2" t="n"/>
-      <c r="O330" s="2" t="n"/>
-      <c r="P330" s="2" t="n"/>
+      <c r="O330" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P330" s="2" t="inlineStr">
+        <is>
+          <t>Batcham</t>
+        </is>
+      </c>
       <c r="Q330" s="2" t="n"/>
       <c r="R330" s="2" t="n"/>
       <c r="S330" s="2" t="n"/>
@@ -34111,10 +37677,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M331" s="2" t="n"/>
+      <c r="M331" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N331" s="2" t="n"/>
-      <c r="O331" s="2" t="n"/>
-      <c r="P331" s="2" t="n"/>
+      <c r="O331" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P331" s="2" t="inlineStr">
+        <is>
+          <t>Foumbot</t>
+        </is>
+      </c>
       <c r="Q331" s="2" t="n"/>
       <c r="R331" s="2" t="n"/>
       <c r="S331" s="2" t="n"/>
@@ -34213,10 +37791,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M332" s="2" t="n"/>
+      <c r="M332" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N332" s="2" t="n"/>
-      <c r="O332" s="2" t="n"/>
-      <c r="P332" s="2" t="n"/>
+      <c r="O332" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P332" s="2" t="inlineStr">
+        <is>
+          <t>Penka-Michel</t>
+        </is>
+      </c>
       <c r="Q332" s="2" t="n"/>
       <c r="R332" s="2" t="n"/>
       <c r="S332" s="2" t="n"/>
@@ -34405,10 +37995,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M334" s="2" t="n"/>
+      <c r="M334" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N334" s="2" t="n"/>
-      <c r="O334" s="2" t="n"/>
-      <c r="P334" s="2" t="n"/>
+      <c r="O334" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P334" s="2" t="inlineStr">
+        <is>
+          <t>Galim</t>
+        </is>
+      </c>
       <c r="Q334" s="2" t="n"/>
       <c r="R334" s="2" t="n"/>
       <c r="S334" s="2" t="n"/>
@@ -34507,10 +38109,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M335" s="2" t="n"/>
+      <c r="M335" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N335" s="2" t="n"/>
-      <c r="O335" s="2" t="n"/>
-      <c r="P335" s="2" t="n"/>
+      <c r="O335" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P335" s="2" t="inlineStr">
+        <is>
+          <t>Koutaba</t>
+        </is>
+      </c>
       <c r="Q335" s="2" t="n"/>
       <c r="R335" s="2" t="n"/>
       <c r="S335" s="2" t="n"/>
@@ -34609,10 +38223,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M336" s="2" t="n"/>
+      <c r="M336" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N336" s="2" t="n"/>
-      <c r="O336" s="2" t="n"/>
-      <c r="P336" s="2" t="n"/>
+      <c r="O336" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P336" s="2" t="inlineStr">
+        <is>
+          <t>Kouoptamo</t>
+        </is>
+      </c>
       <c r="Q336" s="2" t="n"/>
       <c r="R336" s="2" t="n"/>
       <c r="S336" s="2" t="n"/>
@@ -34711,10 +38337,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M337" s="2" t="n"/>
+      <c r="M337" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N337" s="2" t="n"/>
-      <c r="O337" s="2" t="n"/>
-      <c r="P337" s="2" t="n"/>
+      <c r="O337" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P337" s="2" t="inlineStr">
+        <is>
+          <t>Malentouen</t>
+        </is>
+      </c>
       <c r="Q337" s="2" t="n"/>
       <c r="R337" s="2" t="n"/>
       <c r="S337" s="2" t="n"/>
@@ -34903,10 +38541,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M339" s="2" t="n"/>
+      <c r="M339" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N339" s="2" t="n"/>
-      <c r="O339" s="2" t="n"/>
-      <c r="P339" s="2" t="n"/>
+      <c r="O339" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P339" s="2" t="inlineStr">
+        <is>
+          <t>Massangam</t>
+        </is>
+      </c>
       <c r="Q339" s="2" t="n"/>
       <c r="R339" s="2" t="n"/>
       <c r="S339" s="2" t="n"/>
@@ -35005,10 +38655,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M340" s="2" t="n"/>
+      <c r="M340" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N340" s="2" t="n"/>
-      <c r="O340" s="2" t="n"/>
-      <c r="P340" s="2" t="n"/>
+      <c r="O340" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P340" s="2" t="inlineStr">
+        <is>
+          <t>Santchou</t>
+        </is>
+      </c>
       <c r="Q340" s="2" t="n"/>
       <c r="R340" s="2" t="n"/>
       <c r="S340" s="2" t="n"/>
@@ -35107,10 +38769,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M341" s="2" t="n"/>
+      <c r="M341" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N341" s="2" t="n"/>
-      <c r="O341" s="2" t="n"/>
-      <c r="P341" s="2" t="n"/>
+      <c r="O341" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P341" s="2" t="inlineStr">
+        <is>
+          <t>Babadjou</t>
+        </is>
+      </c>
       <c r="Q341" s="2" t="n"/>
       <c r="R341" s="2" t="n"/>
       <c r="S341" s="2" t="n"/>
@@ -35209,10 +38883,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M342" s="2" t="n"/>
+      <c r="M342" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N342" s="2" t="n"/>
-      <c r="O342" s="2" t="n"/>
-      <c r="P342" s="2" t="n"/>
+      <c r="O342" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P342" s="2" t="inlineStr">
+        <is>
+          <t>Magba</t>
+        </is>
+      </c>
       <c r="Q342" s="2" t="n"/>
       <c r="R342" s="2" t="n"/>
       <c r="S342" s="2" t="n"/>
@@ -35311,10 +38997,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M343" s="2" t="n"/>
+      <c r="M343" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N343" s="2" t="n"/>
-      <c r="O343" s="2" t="n"/>
-      <c r="P343" s="2" t="n"/>
+      <c r="O343" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P343" s="2" t="inlineStr">
+        <is>
+          <t>Bamendjou</t>
+        </is>
+      </c>
       <c r="Q343" s="2" t="n"/>
       <c r="R343" s="2" t="n"/>
       <c r="S343" s="2" t="n"/>
@@ -35413,10 +39111,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M344" s="2" t="n"/>
+      <c r="M344" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N344" s="2" t="n"/>
-      <c r="O344" s="2" t="n"/>
-      <c r="P344" s="2" t="n"/>
+      <c r="O344" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P344" s="2" t="inlineStr">
+        <is>
+          <t>Kékem</t>
+        </is>
+      </c>
       <c r="Q344" s="2" t="n"/>
       <c r="R344" s="2" t="n"/>
       <c r="S344" s="2" t="n"/>
@@ -35515,10 +39225,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M345" s="2" t="n"/>
+      <c r="M345" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N345" s="2" t="n"/>
-      <c r="O345" s="2" t="n"/>
-      <c r="P345" s="2" t="n"/>
+      <c r="O345" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P345" s="2" t="inlineStr">
+        <is>
+          <t>Bandja</t>
+        </is>
+      </c>
       <c r="Q345" s="2" t="n"/>
       <c r="R345" s="2" t="n"/>
       <c r="S345" s="2" t="n"/>
@@ -35617,10 +39339,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M346" s="2" t="n"/>
+      <c r="M346" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N346" s="2" t="n"/>
-      <c r="O346" s="2" t="n"/>
-      <c r="P346" s="2" t="n"/>
+      <c r="O346" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P346" s="2" t="inlineStr">
+        <is>
+          <t>Bangourain</t>
+        </is>
+      </c>
       <c r="Q346" s="2" t="n"/>
       <c r="R346" s="2" t="n"/>
       <c r="S346" s="2" t="n"/>
@@ -35719,10 +39453,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M347" s="2" t="n"/>
+      <c r="M347" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N347" s="2" t="n"/>
-      <c r="O347" s="2" t="n"/>
-      <c r="P347" s="2" t="n"/>
+      <c r="O347" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P347" s="2" t="inlineStr">
+        <is>
+          <t>Banka</t>
+        </is>
+      </c>
       <c r="Q347" s="2" t="n"/>
       <c r="R347" s="2" t="n"/>
       <c r="S347" s="2" t="n"/>
@@ -35821,10 +39567,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M348" s="2" t="n"/>
+      <c r="M348" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N348" s="2" t="n"/>
-      <c r="O348" s="2" t="n"/>
-      <c r="P348" s="2" t="n"/>
+      <c r="O348" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P348" s="2" t="inlineStr">
+        <is>
+          <t>Njimom</t>
+        </is>
+      </c>
       <c r="Q348" s="2" t="n"/>
       <c r="R348" s="2" t="n"/>
       <c r="S348" s="2" t="n"/>
@@ -35923,10 +39681,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M349" s="2" t="n"/>
+      <c r="M349" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N349" s="2" t="n"/>
-      <c r="O349" s="2" t="n"/>
-      <c r="P349" s="2" t="n"/>
+      <c r="O349" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P349" s="2" t="inlineStr">
+        <is>
+          <t>Baham</t>
+        </is>
+      </c>
       <c r="Q349" s="2" t="n"/>
       <c r="R349" s="2" t="n"/>
       <c r="S349" s="2" t="n"/>
@@ -36025,10 +39795,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M350" s="2" t="n"/>
+      <c r="M350" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N350" s="2" t="n"/>
-      <c r="O350" s="2" t="n"/>
-      <c r="P350" s="2" t="n"/>
+      <c r="O350" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P350" s="2" t="inlineStr">
+        <is>
+          <t>Fongo-Tongo</t>
+        </is>
+      </c>
       <c r="Q350" s="2" t="n"/>
       <c r="R350" s="2" t="n"/>
       <c r="S350" s="2" t="n"/>
@@ -36127,10 +39909,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M351" s="2" t="n"/>
+      <c r="M351" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N351" s="2" t="n"/>
-      <c r="O351" s="2" t="n"/>
-      <c r="P351" s="2" t="n"/>
+      <c r="O351" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P351" s="2" t="inlineStr">
+        <is>
+          <t>Bangou</t>
+        </is>
+      </c>
       <c r="Q351" s="2" t="n"/>
       <c r="R351" s="2" t="n"/>
       <c r="S351" s="2" t="n"/>
@@ -36229,10 +40023,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M352" s="2" t="n"/>
+      <c r="M352" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N352" s="2" t="n"/>
-      <c r="O352" s="2" t="n"/>
-      <c r="P352" s="2" t="n"/>
+      <c r="O352" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P352" s="2" t="inlineStr">
+        <is>
+          <t>Bazou</t>
+        </is>
+      </c>
       <c r="Q352" s="2" t="n"/>
       <c r="R352" s="2" t="n"/>
       <c r="S352" s="2" t="n"/>
@@ -36331,10 +40137,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M353" s="2" t="n"/>
+      <c r="M353" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N353" s="2" t="n"/>
-      <c r="O353" s="2" t="n"/>
-      <c r="P353" s="2" t="n"/>
+      <c r="O353" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P353" s="2" t="inlineStr">
+        <is>
+          <t>Tonga</t>
+        </is>
+      </c>
       <c r="Q353" s="2" t="n"/>
       <c r="R353" s="2" t="n"/>
       <c r="S353" s="2" t="n"/>
@@ -36433,10 +40251,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M354" s="2" t="n"/>
+      <c r="M354" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N354" s="2" t="n"/>
-      <c r="O354" s="2" t="n"/>
-      <c r="P354" s="2" t="n"/>
+      <c r="O354" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P354" s="2" t="inlineStr">
+        <is>
+          <t>Bayangam</t>
+        </is>
+      </c>
       <c r="Q354" s="2" t="n"/>
       <c r="R354" s="2" t="n"/>
       <c r="S354" s="2" t="n"/>
@@ -36535,10 +40365,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M355" s="2" t="n"/>
+      <c r="M355" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N355" s="2" t="n"/>
-      <c r="O355" s="2" t="n"/>
-      <c r="P355" s="2" t="n"/>
+      <c r="O355" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P355" s="2" t="inlineStr">
+        <is>
+          <t>Banwa</t>
+        </is>
+      </c>
       <c r="Q355" s="2" t="n"/>
       <c r="R355" s="2" t="n"/>
       <c r="S355" s="2" t="n"/>
@@ -36727,10 +40569,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M357" s="2" t="n"/>
+      <c r="M357" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N357" s="2" t="n"/>
-      <c r="O357" s="2" t="n"/>
-      <c r="P357" s="2" t="n"/>
+      <c r="O357" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P357" s="2" t="inlineStr">
+        <is>
+          <t>Batié</t>
+        </is>
+      </c>
       <c r="Q357" s="2" t="n"/>
       <c r="R357" s="2" t="n"/>
       <c r="S357" s="2" t="n"/>
@@ -36829,10 +40683,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M358" s="2" t="n"/>
+      <c r="M358" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N358" s="2" t="n"/>
-      <c r="O358" s="2" t="n"/>
-      <c r="P358" s="2" t="n"/>
+      <c r="O358" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P358" s="2" t="inlineStr">
+        <is>
+          <t>Bana</t>
+        </is>
+      </c>
       <c r="Q358" s="2" t="n"/>
       <c r="R358" s="2" t="n"/>
       <c r="S358" s="2" t="n"/>
@@ -36931,10 +40797,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M359" s="2" t="n"/>
+      <c r="M359" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N359" s="2" t="n"/>
-      <c r="O359" s="2" t="n"/>
-      <c r="P359" s="2" t="n"/>
+      <c r="O359" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P359" s="2" t="inlineStr">
+        <is>
+          <t>Fokoué</t>
+        </is>
+      </c>
       <c r="Q359" s="2" t="n"/>
       <c r="R359" s="2" t="n"/>
       <c r="S359" s="2" t="n"/>
@@ -37033,10 +40911,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M360" s="2" t="n"/>
+      <c r="M360" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N360" s="2" t="n"/>
-      <c r="O360" s="2" t="n"/>
-      <c r="P360" s="2" t="n"/>
+      <c r="O360" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P360" s="2" t="inlineStr">
+        <is>
+          <t>Bakou</t>
+        </is>
+      </c>
       <c r="Q360" s="2" t="n"/>
       <c r="R360" s="2" t="n"/>
       <c r="S360" s="2" t="n"/>
@@ -37135,10 +41025,22 @@
           <t>WestCameroon</t>
         </is>
       </c>
-      <c r="M361" s="2" t="n"/>
+      <c r="M361" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N361" s="2" t="n"/>
-      <c r="O361" s="2" t="n"/>
-      <c r="P361" s="2" t="n"/>
+      <c r="O361" s="2" t="inlineStr">
+        <is>
+          <t>CM-OU</t>
+        </is>
+      </c>
+      <c r="P361" s="2" t="inlineStr">
+        <is>
+          <t>Bassamba</t>
+        </is>
+      </c>
       <c r="Q361" s="2" t="n"/>
       <c r="R361" s="2" t="n"/>
       <c r="S361" s="2" t="n"/>
